--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,20 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,7 +146,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,13 +158,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -784,29 +775,29 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>569.8</v>
-      </c>
-      <c r="D4" s="11" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="12" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n"/>
       <c r="I4" s="3" t="n">
-        <v>72.8</v>
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
@@ -815,13 +806,13 @@
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
+        <v>32.3</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>13.7</v>
+        <v>13.2</v>
       </c>
       <c r="S4" s="3" t="n">
         <v>4.3</v>
@@ -829,23 +820,23 @@
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="8" t="n">
+      <c r="U4" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W4" s="8" t="n">
-        <v>10.3</v>
+      <c r="W4" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X4" s="3" t="n">
         <v>6.5</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>12.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -860,22 +851,28 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>856143513.2</v>
-      </c>
-      <c r="D5" s="11" t="n">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E5" s="11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
@@ -889,10 +886,10 @@
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>15.5</v>
+        <v>35.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>21.6</v>
+        <v>0.4</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -901,19 +898,19 @@
         <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.7</v>
+        <v>31.2</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>5.7</v>
+        <v>57.2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>41</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.2</v>
@@ -925,10 +922,10 @@
         <v>8.1</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>201.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>3.1</v>
+        <v>80.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -943,18 +940,24 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>856143513.2</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E6" s="3" t="n">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+2
+</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="8" t="n">
-        <v>31.9</v>
+      <c r="F6" s="12" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -963,25 +966,25 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>13.2</v>
+        <v>12.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
-        <v>12.2</v>
+      <c r="L6" s="13" t="n">
+        <v>488.7</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>2.8</v>
+        <v>8.4</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>18.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q6" s="3" t="n">
         <v>32.7</v>
@@ -990,7 +993,7 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>14.4</v>
@@ -1002,10 +1005,10 @@
         <v>28.9</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>16.3</v>
@@ -1027,22 +1030,22 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>583.6</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G7" s="3" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
+        <v>2.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1051,7 +1054,7 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
@@ -1060,16 +1063,16 @@
         <v>5.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
+        <v>39.7</v>
       </c>
       <c r="R7" s="3" t="n">
         <v>13.8</v>
@@ -1090,10 +1093,10 @@
         <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>15.2</v>
+        <v>12.2</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>3.3</v>
@@ -1112,39 +1115,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>34.4</v>
-      </c>
+        <v>25.1</v>
+      </c>
+      <c r="D8" s="9" t="n"/>
       <c r="E8" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>22.7</v>
+        <v>2.2</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>22.2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>11</v>
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>27.2</v>
       </c>
       <c r="I8" s="3" t="n"/>
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>110.8</v>
+        <v>2.2</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>36.5</v>
+        <v>0.8</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>26.2</v>
+        <v>26.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1156,7 +1157,7 @@
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1165,13 +1166,13 @@
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>5.4</v>
+        <v>1.5</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>15.3</v>
+        <v>5.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="Y8" s="3" t="n">
         <v>22.1</v>
@@ -1193,19 +1194,27 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="F9" s="10" t="n"/>
+        <v>2656.2</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>111.4</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2262
+411464141
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="n">
         <v>44.2</v>
       </c>
@@ -1213,48 +1222,48 @@
         <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n">
-        <v>28.8</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183.8</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>165</v>
+        <v>1685</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>71.8</v>
+        <v>24.8</v>
       </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n">
         <v>55.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>224.1</v>
+        <v>24.1</v>
       </c>
       <c r="V9" s="3" t="n">
         <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>38.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>106.2</v>
+        <v>16.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>20.2</v>
+        <v>90.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1270,15 +1279,15 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>534.4</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F10" s="12" t="n">
         <v>22.3</v>
       </c>
       <c r="G10" s="3" t="n">
@@ -1291,24 +1300,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>13.7</v>
+        <v>2.7</v>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="n">
-        <v>13.4</v>
+      <c r="L10" s="3" t="n">
+        <v>3.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>3.2</v>
+        <v>32.6</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>36.6</v>
+      </c>
+      <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
@@ -1316,28 +1323,28 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>13.9</v>
+        <v>2.9</v>
+      </c>
+      <c r="W10" s="13" t="n">
+        <v>38.2</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>17.8</v>
+        <v>0.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>184.1</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>150.2</v>
+        <v>11.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1353,25 +1360,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>427.9</v>
+        <v>422.9</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>23.7</v>
+        <v>42.1</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
+        <v>41.1</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
@@ -1383,14 +1390,18 @@
       <c r="M11" s="3" t="n">
         <v>6.5</v>
       </c>
-      <c r="N11" s="3" t="n">
-        <v>0.2</v>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+8
+</t>
+        </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
@@ -1400,22 +1411,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
+        <v>229</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>81</v>
+        <v>31.9</v>
       </c>
       <c r="V11" s="3" t="n">
         <v>21.7</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>47</v>
+        <v>424</v>
       </c>
       <c r="Z11" s="3" t="n"/>
       <c r="AA11" s="3" t="inlineStr">
@@ -1431,26 +1442,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5 6
-</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>31.6</v>
+      <c r="C12" s="3" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>11.9</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="F12" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="11" t="n">
-        <v>19.9</v>
+      <c r="G12" s="13" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>2.2</v>
+        <v>14.8</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>6.1</v>
@@ -1459,7 +1467,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1468,7 +1476,7 @@
         <v>6.4</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
@@ -1476,35 +1484,37 @@
       <c r="P12" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="8" t="n">
-        <v>10.8</v>
+      <c r="Q12" s="3" t="n">
+        <v>31.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>29.2</v>
+        <v>92.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y12" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Z12" s="3" t="n">
-        <v>5.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Y12" s="3" t="n"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+76
+</t>
+        </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1520,21 +1530,21 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>601.3</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E13" s="11" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G13" s="11" t="n">
+      <c r="F13" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="I13" s="3" t="n">
@@ -1553,19 +1563,19 @@
         <v>12.7</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>0.9</v>
+        <v>11.7</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
+        <v>39.6</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15.3</v>
+      <c r="R13" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1574,19 +1584,19 @@
         <v>13.5</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>28.7</v>
+        <v>49.6</v>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>87.2</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="Z13" s="3" t="n"/>
       <c r="AA13" s="3" t="inlineStr">
@@ -1605,19 +1615,19 @@
       <c r="C14" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E14" s="11" t="n">
+      <c r="D14" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="F14" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1627,43 +1637,43 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>1.8</v>
+        <v>2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>49.5</v>
+        <v>9.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="R14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>1.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>27</v>
+        <v>41.2</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>14.4</v>
+        <v>4.4</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>9.199999999999999</v>
@@ -1688,16 +1698,16 @@
       <c r="C15" s="3" t="n">
         <v>552.4</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>31.2</v>
+      <c r="D15" s="3" t="n">
+        <v>34.3</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>15</v>
+        <v>79.5</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G15" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1710,16 +1720,16 @@
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>48</v>
@@ -1730,11 +1740,11 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="8" t="n">
-        <v>14.3</v>
+      <c r="R15" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>15.4</v>
@@ -1743,7 +1753,7 @@
         <v>38</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>14</v>
@@ -1755,7 +1765,7 @@
         <v>23.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1771,16 +1781,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9572.1</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1189.6</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>82.09999999999999</v>
+        <v>2577.7</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>8.1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1789,29 +1799,39 @@
         <v>10.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>3.3</v>
+        <v>35.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>11.7</v>
+        <v>5.4</v>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1811
+14
+</t>
+        </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>89.09999999999999</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>822.3</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">443222
+181909191
+</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>212.5</v>
+        <v>2121.5</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>82.2</v>
+        <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>54.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>23.6</v>
@@ -1820,23 +1840,29 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="U16" s="3" t="n"/>
+        <v>820.6</v>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+7918949
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="n">
         <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>148.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>11.5</v>
+        <v>19.1</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1852,74 +1878,74 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>15.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>26.8</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G17" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>61.8</v>
+        <v>6.8</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K17" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="L17" s="3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="N17" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="n">
         <v>42.5</v>
       </c>
-      <c r="P17" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>30.9</v>
+      <c r="P17" s="13" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="Q17" s="13" t="n">
+        <v>60.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0.1</v>
+        <v>4.4</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>7.3</v>
+        <v>72.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>96.3</v>
+        <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>22.1</v>
+        <v>212.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,63 +1960,62 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
-        <v>552.1</v>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">521
+2
+</t>
+        </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12 7
-</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n"/>
+        <v>34.9</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F18" s="9" t="n"/>
       <c r="G18" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="K18" s="3" t="n"/>
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>10.4</v>
+        <v>16.4</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>1.1</v>
+        <v>32.9</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>37.6</v>
+        <v>166.9</v>
+      </c>
+      <c r="U18" s="13" t="n">
+        <v>72.59999999999999</v>
       </c>
       <c r="V18" s="3" t="n">
         <v>28.1</v>
@@ -2005,7 +2030,7 @@
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2020,23 +2045,27 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>326.4</v>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+2975
+</t>
+        </is>
       </c>
       <c r="D19" s="11" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E19" s="11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>12.4</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>16.4</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>0.8</v>
@@ -2045,7 +2074,7 @@
         <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>13.5</v>
@@ -2053,19 +2082,17 @@
       <c r="M19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="N19" s="3" t="n">
-        <v>0.7</v>
-      </c>
+      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R19" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2075,19 +2102,19 @@
         <v>12.8</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>20.4</v>
+        <v>4.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.2</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="Z19" s="3" t="n"/>
       <c r="AA19" s="3" t="inlineStr">
@@ -2103,15 +2130,20 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D20" s="13" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">446466240
+212
+79719019
+</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n">
         <v>12.3</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.3</v>
+        <v>12.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2120,34 +2152,34 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>32</v>
+        <v>28.3</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2156,15 +2188,17 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>41.4</v>
+        <v>4.4</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="X20" s="3" t="n"/>
+      <c r="X20" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="Y20" s="3" t="n">
         <v>32</v>
       </c>
@@ -2183,59 +2217,61 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.9</v>
-      </c>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F21" s="3" t="n">
+        <v>542.2</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F21" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>5.5</v>
+      <c r="G21" s="12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <v>23.1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>25.6</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>10.5</v>
+        <v>11.9</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>492</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>28.3</v>
+        <v>30.7</v>
       </c>
       <c r="R21" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>2.6</v>
+        <v>12.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>29.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V21" s="3" t="n">
         <v>26.3</v>
@@ -2250,7 +2286,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2266,16 +2302,16 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>516.3</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>3.6</v>
+        <v>536.3</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>34.1</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>22.5</v>
+      <c r="F22" s="11" t="n">
+        <v>43.5</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>16.6</v>
@@ -2284,31 +2320,31 @@
         <v>13.3</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="J22" s="8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>51</v>
+        <v>21.1</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>30.7</v>
+        <v>22.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>4.5</v>
@@ -2317,19 +2353,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
+        <v>14.9</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="V22" s="3" t="n">
-        <v>98.2</v>
+        <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>9.4</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2348,63 +2384,67 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>2547.5</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>117.1</v>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="10" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>17.1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>11.6</v>
+        <v>86.8</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44255
+82947
+</t>
+        </is>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="K23" s="3" t="n"/>
+        <v>7.2</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>10.7</v>
+        <v>1.1</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>23</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>44.2</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>31.3</v>
+        <v>5.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>7.2</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>29</v>
+        <v>292</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.5</v>
+        <v>30.5</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>68.8</v>
@@ -2413,9 +2453,11 @@
         <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>127.3</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
+        <v>17.3</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>192.1</v>
+      </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2430,51 +2472,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5032.1</v>
-      </c>
-      <c r="D24" s="9" t="n">
+        <v>5026.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="14" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>17.4</v>
+      <c r="E24" s="11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>78.40000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="L24" s="8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>50.3</v>
+        <v>5.3</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>54.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="8" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="R24" s="8" t="n">
+      <c r="Q24" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2483,11 +2525,11 @@
       <c r="T24" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="U24" s="8" t="n">
+      <c r="U24" s="13" t="n">
         <v>87.2</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
@@ -2496,10 +2538,10 @@
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.5</v>
+        <v>2.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>16.6</v>
+        <v>22.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2515,68 +2557,77 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>31.9</v>
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>21.9</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>14.9</v>
+        <v>4.2</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G25" s="8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>2.1</v>
+      </c>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
+        <v>12.1</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
+        <v>400.8</v>
       </c>
       <c r="P25" s="3" t="n">
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>14.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.4</v>
       </c>
       <c r="S25" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="n">
-        <v>88.8</v>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+2
+</t>
+        </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 6 11558
+          <t xml:space="preserve">182
+171111
 </t>
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>45.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z25" s="3" t="n"/>
       <c r="AA25" s="3" t="inlineStr">
@@ -2595,39 +2646,41 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>44.8</v>
+      <c r="E26" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>24.8</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
+        <v>15.5</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n">
-        <v>10.9</v>
+        <v>72.3</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K26" s="13" t="n">
+        <v>8.9</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>1.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
@@ -2639,25 +2692,25 @@
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="U26" s="8" t="n">
-        <v>2823.4</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>4.8</v>
+      <c r="U26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V26" s="13" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="W26" s="13" t="n">
+        <v>49.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Z26" s="3" t="n"/>
       <c r="AA26" s="3" t="inlineStr">
@@ -2674,30 +2727,32 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
+        <v>5.1</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E27" s="11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>23.3</v>
+        <v>28.58</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I27" s="8" t="n">
-        <v>681.6</v>
-      </c>
-      <c r="J27" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2705,13 +2760,13 @@
         <v>10.5</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.9</v>
+        <v>98.5</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1322</v>
+        <v>528</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>82.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>29.3</v>
@@ -2720,28 +2775,32 @@
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>18</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v>28.2</v>
+        <v>3.4</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>22.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>44.3</v>
+        <v>4.2</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>264.4</v>
-      </c>
-      <c r="Z27" s="3" t="n">
-        <v>20.8</v>
+        <v>26.6</v>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2759,74 +2818,78 @@
       <c r="C28" s="3" t="n">
         <v>621</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>23.5</v>
+      <c r="D28" s="3" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>6.5</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="J28" s="8" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>47</v>
+        <v>428</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R28" s="8" t="n">
+      <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>22.5</v>
+        <v>43.4</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>7.2</v>
+        <v>13.2</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>1.3</v>
+        <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>6.9</v>
+        <v>0.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>20.8</v>
+        <v>126.5</v>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+309
+</t>
+        </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2842,31 +2905,31 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
+        <v>0.6</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>34.4</v>
+        <v>3.4</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F29" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2875,10 +2938,10 @@
         <v>10.2</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>41.3</v>
+        <v>4.3</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2886,16 +2949,18 @@
       <c r="Q29" s="3" t="n">
         <v>32.1</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U29" s="3" t="n"/>
+        <v>9.4</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>43.4</v>
+      </c>
       <c r="V29" s="3" t="n">
         <v>27.7</v>
       </c>
@@ -2923,73 +2988,73 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>624.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
-        <v>1561.6</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="E30" s="10" t="n">
         <v>12.2</v>
       </c>
-      <c r="F30" s="9" t="n">
-        <v>29.3</v>
+      <c r="F30" s="10" t="n">
+        <v>2.3</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>87.09999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>35.8</v>
+        <v>55.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>81.8</v>
+        <v>0</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.9</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>83.5</v>
+        <v>33.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>10.9</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>66.8</v>
+        <v>6.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42</v>
+        <v>42.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>18.6</v>
+        <v>28.3</v>
       </c>
       <c r="Z30" s="3" t="n"/>
       <c r="AA30" s="3" t="inlineStr">
@@ -3006,31 +3071,31 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="11" t="n">
+        <v>556.4</v>
+      </c>
+      <c r="D31" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>18</v>
+      <c r="E31" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>18.4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>4.7</v>
+        <v>0.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>522.4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="8" t="n">
-        <v>18.9</v>
+      <c r="K31" s="13" t="n">
+        <v>92.90000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3044,21 +3109,19 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="8" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>14.2</v>
+      <c r="P31" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="R31" s="13" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>82.59999999999999</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="T31" s="3" t="n"/>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
@@ -3072,7 +3135,7 @@
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>28.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3090,36 +3153,32 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F32" s="3" t="n">
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="12" t="n">
         <v>23.6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>11.4</v>
-      </c>
+        <v>23.2</v>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="n">
-        <v>16.4</v>
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>0.8</v>
@@ -3137,27 +3196,27 @@
         <v>4.1</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="T32" s="3" t="n"/>
+        <v>4.7</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="U32" s="3" t="n">
-        <v>42.4</v>
+        <v>424.1</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>1.5</v>
+        <v>28.5</v>
       </c>
       <c r="W32" s="3" t="n">
-        <v>11.3</v>
+        <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>24.6</v>
-      </c>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3171,14 +3230,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>10.6</v>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="11" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1.6</v>
       </c>
       <c r="F33" s="3" t="n">
         <v>22.2</v>
@@ -3187,58 +3244,58 @@
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>15.8</v>
+        <v>35.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>0.6</v>
+        <v>5.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141.8</v>
+        <v>4.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>12.8</v>
+        <v>11.8</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R33" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="S33" s="3" t="n">
-        <v>10.2</v>
+      <c r="R33" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="S33" s="13" t="n">
+        <v>6.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="U33" s="8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U33" s="3" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
+        <v>44.5</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>11.9</v>
+        <v>1.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="Z33" s="3" t="n"/>
       <c r="AA33" s="3" t="inlineStr">
@@ -3257,13 +3314,13 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="F34" s="3" t="n">
+      <c r="D34" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="G34" s="3" t="n">
@@ -3273,7 +3330,7 @@
         <v>1.1</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3282,10 +3339,10 @@
         <v>6</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>41.2</v>
+        <v>17.2</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0.8</v>
@@ -3297,13 +3354,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>3.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>2.1</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>30.3</v>
@@ -3318,13 +3375,17 @@
         <v>12.7</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z34" s="3" t="n">
-        <v>10.8</v>
+        <v>5</v>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+178
+</t>
+        </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3340,28 +3401,28 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>437.9</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>23.2</v>
+        <v>433.9</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>32.9</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>19.1</v>
+        <v>12.4</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>14.2</v>
@@ -3370,14 +3431,16 @@
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N35" s="3" t="n"/>
+        <v>1.4</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>10.3</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>24</v>
+        <v>2.1</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>9.6</v>
+        <v>2.6</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>19</v>
@@ -3389,26 +3452,24 @@
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>2.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>10.8</v>
-      </c>
+        <v>43.1</v>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3423,18 +3484,18 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>222.2</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="E36" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G36" s="11" t="n">
+      <c r="E36" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="H36" s="3" t="n">
@@ -3444,10 +3505,10 @@
         <v>4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K36" s="8" t="n">
-        <v>14.5</v>
+        <v>9.1</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>44.2</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
@@ -3455,14 +3516,12 @@
       <c r="M36" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>19.2</v>
+        <v>29.2</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>30.8</v>
@@ -3471,25 +3530,25 @@
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>1.2</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>28.2</v>
+        <v>21.6</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>12.2</v>
+        <v>1.6</v>
       </c>
       <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
@@ -3505,57 +3564,53 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
-        <v>222.2</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>151.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G37" s="14" t="n">
-        <v>11.1</v>
+      <c r="C37" s="3" t="n"/>
+      <c r="D37" s="10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>11.2</v>
+        <v>42.4</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>21.6</v>
+        <v>41.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.4</v>
+        <v>9.1</v>
       </c>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>821.9</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N37" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>240.2</v>
+        <v>20.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>389.8</v>
+        <v>59.8</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>82.2</v>
+        <v>0.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>4.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>124.9</v>
+        <v>34.1</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>3.4</v>
@@ -3564,15 +3619,17 @@
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>4.9</v>
+        <v>49.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>183.1</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>96.2</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3589,26 +3646,26 @@
       <c r="C38" s="3" t="n">
         <v>43.3</v>
       </c>
-      <c r="D38" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="E38" s="14" t="n">
+      <c r="D38" s="11" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="E38" s="11" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="F38" s="9" t="n">
-        <v>10.3</v>
+      <c r="F38" s="10" t="n">
+        <v>16.3</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>55.8</v>
+        <v>5.8</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>301</v>
+      <c r="J38" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>36.1</v>
@@ -3617,43 +3674,43 @@
         <v>16.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>13.2</v>
+        <v>53.2</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>4.7</v>
+        <v>47.8</v>
       </c>
       <c r="O38" s="3" t="n">
         <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="R38" s="3" t="n">
-        <v>14.5</v>
+        <v>59.8</v>
+      </c>
+      <c r="Q38" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R38" s="13" t="n">
+        <v>48.5</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>151</v>
+        <v>11.6</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>28.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>22.8</v>
+        <v>2.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>13.4</v>
+        <v>12.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>9.9</v>
+        <v>0.2</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3672,39 +3729,41 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.1</v>
+        <v>5444.4</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>29.2</v>
+        <v>30.35</v>
       </c>
       <c r="E39" s="11" t="n">
-        <v>13.8</v>
+        <v>1.8</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>21.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H39" s="8" t="n">
-        <v>12.1</v>
+        <v>6.5</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.2</v>
+        <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>5.7</v>
+      </c>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M39" s="8" t="n">
-        <v>6000.4</v>
+      <c r="M39" s="3" t="n">
+        <v>40.6</v>
       </c>
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3719,25 +3778,25 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>20.3</v>
+        <v>0.2</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>29.4</v>
+        <v>2.4</v>
       </c>
       <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="W39" s="8" t="n">
-        <v>15</v>
+      <c r="W39" s="3" t="n">
+        <v>5</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3753,43 +3812,41 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D40" s="12" t="n">
         <v>29.2</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="12" t="n">
         <v>21.7</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>51.2</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>16.2</v>
-      </c>
+      <c r="K40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="3" t="n"/>
       <c r="M40" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>2.4</v>
+        <v>94.8</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
@@ -3797,14 +3854,14 @@
       <c r="Q40" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="R40" s="8" t="n">
-        <v>15</v>
+      <c r="R40" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>6.1</v>
+        <v>10</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>822.4</v>
+        <v>22.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>34.2</v>
@@ -3816,13 +3873,13 @@
         <v>14.7</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>31.6</v>
+        <v>21</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>28.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3838,76 +3895,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E41" s="11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E41" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G41" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>11.2</v>
+        <v>2.7</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>18.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>10.4</v>
+        <v>1.4</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>9.5</v>
+        <v>23.8</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>10.8</v>
+        <v>52</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>19.5</v>
+        <v>197.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>32.6</v>
+        <v>2.6</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>10.1</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>828.9</v>
+        <v>28.9</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>223.6</v>
+        <v>16.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3922,77 +3979,81 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="D42" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G42" s="11" t="n">
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+4811
+</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G42" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>53</v>
+      <c r="H42" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>18.3</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K42" s="3" t="n">
-        <v>10</v>
+      <c r="K42" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>11.9</v>
+        <v>18.8</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>13.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>19.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="R42" s="3" t="n">
-        <v>4.1</v>
+        <v>45.5</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>22.2</v>
+        <v>2.2</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>24.6</v>
+        <v>2.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>19</v>
+        <v>22.5</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>82.8</v>
+        <v>5.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>165.5</v>
+        <v>16.4</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4008,76 +4069,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="E43" s="11" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F43" s="11" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G43" s="11" t="n">
+      <c r="E43" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G43" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>17.7</v>
+        <v>16.8</v>
       </c>
       <c r="M43" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>9.5</v>
+        <v>98.5</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>21.5</v>
+        <v>58</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q43" s="3" t="n">
-        <v>76.2</v>
-      </c>
+        <v>9.6</v>
+      </c>
+      <c r="Q43" s="3" t="n"/>
       <c r="R43" s="3" t="n">
-        <v>4.2</v>
+        <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>24.6</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>45.1</v>
+        <v>19.9</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X43" s="3" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
+      </c>
+      <c r="X43" s="13" t="n">
+        <v>41.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>25.3</v>
+        <v>285.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.8</v>
+        <v>16.5</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4093,76 +4152,76 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>258</v>
+        <v>23.9</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="F44" s="11" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F44" s="3" t="n">
         <v>23.5</v>
       </c>
-      <c r="G44" s="8" t="n">
-        <v>14.9</v>
+      <c r="G44" s="3" t="n">
+        <v>4.4</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>19.7</v>
+        <v>5.6</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>16.6</v>
+        <v>17.7</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10.5</v>
+        <v>16.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>1.4</v>
+        <v>581.5</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>2.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q44" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R44" s="8" t="n">
-        <v>84.40000000000001</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>7.8</v>
+      <c r="R44" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S44" s="13" t="n">
+        <v>89.8</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>1.4</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>14.7</v>
+        <v>13.5</v>
       </c>
       <c r="X44" s="3" t="n">
-        <v>12.9</v>
+        <v>8.4</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4178,76 +4237,78 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>231.2</v>
-      </c>
-      <c r="D45" s="11" t="n">
+        <v>58</v>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="F45" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G45" s="11" t="n">
+      <c r="G45" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.9</v>
+        <v>119.1</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>356</v>
+        <v>6.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>9</v>
+        <v>90.8</v>
       </c>
       <c r="K45" s="3" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>181.1</v>
+        <v>16.6</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>119.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>226.5</v>
+        <v>0.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>18.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>91.2</v>
+        <v>22.2</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>881.8</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>2.1</v>
-      </c>
+        <v>14.4</v>
+      </c>
+      <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n">
-        <v>19.2</v>
+        <v>2.2</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>72.2</v>
+        <v>52.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>75.2</v>
+        <v>21.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>186.5</v>
+        <v>14.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>184.1</v>
+        <v>1.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>222.1</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>19.6</v>
+        <v>2.2</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+11
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4263,70 +4324,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>139.9</v>
+        <v>232.2</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>232.1</v>
       </c>
       <c r="G46" s="3" t="n"/>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>35</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="K46" s="3" t="n"/>
+        <v>524.2</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="L46" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="N46" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>11.1</v>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>26.5</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>2.2</v>
-      </c>
+        <v>78.40000000000001</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="R46" s="13" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n">
-        <v>8.1</v>
+        <v>2.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>30.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>24.8</v>
+        <v>751.9</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>14.4</v>
+        <v>18.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>10.8</v>
+        <v>64.8</v>
       </c>
       <c r="Y46" s="3" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>19.6</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -55,6 +49,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,7 +152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,13 +161,19 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,69 +787,59 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="D4" s="12" t="n">
+        <v>1569.8</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n">
-        <v>2.8</v>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="14" t="n">
+        <v>72.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="n">
         <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>13.2</v>
+      <c r="Q4" s="14" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="R4" s="14" t="n">
+        <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="U4" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="Y4" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -851,33 +853,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>2.8</v>
+      <c r="C5" s="3" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>12.9</v>
+        <v>44.2</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.8</v>
@@ -885,47 +883,45 @@
       <c r="L5" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>35.5</v>
+      <c r="M5" s="14" t="n">
+        <v>65.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>9.1</v>
+        <v>19.1</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="R5" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R5" s="14" t="n">
         <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W5" s="3" t="n">
-        <v>14.2</v>
+        <v>5.7</v>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="14" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="W5" s="14" t="n">
+        <v>10.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>8.1</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>21.2</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>80.8</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -940,24 +936,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-2
-</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E6" s="12" t="n">
+      <c r="C6" s="3" t="n">
+        <v>1504.8</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E6" s="13" t="n">
         <v>10.8</v>
       </c>
-      <c r="F6" s="12" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="F6" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>2062.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -966,55 +958,53 @@
         <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="13" t="n">
-        <v>488.7</v>
-      </c>
       <c r="M6" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>8.4</v>
+        <v>16</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>89.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="P6" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="14" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="14" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>2.1</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>42.4</v>
+        <v>1</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>28.9</v>
+        <v>28.2</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>13.5</v>
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
-        <v>6.8</v>
+        <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>16.3</v>
+        <v>201.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>3.3</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1030,76 +1020,74 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="D7" s="12" t="n">
+        <v>583.6</v>
+      </c>
+      <c r="D7" s="13" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="13" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I7" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I7" s="14" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2</v>
+        <v>46.1</v>
+      </c>
+      <c r="K7" s="14" t="n">
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>54.6</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="n">
-        <v>25</v>
+        <v>22.1</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="R7" s="3" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="R7" s="14" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>51.7</v>
+        <v>4.4</v>
+      </c>
+      <c r="U7" s="14" t="n">
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>28.9</v>
+      </c>
+      <c r="W7" s="14" t="n">
+        <v>13.5</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.1</v>
+        <v>16.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>12.2</v>
+        <v>116.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>3.3</v>
+        <v>33.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1115,37 +1103,37 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
+        <v>485.1</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>91</v>
+      </c>
       <c r="K8" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>26.5</v>
+        <v>236.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1153,32 +1141,32 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="14" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="3" t="n">
-        <v>7.9</v>
+      <c r="S8" s="14" t="n">
+        <v>71</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="U8" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U8" s="14" t="n">
         <v>42.2</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>1.7</v>
+        <v>45.1</v>
+      </c>
+      <c r="W8" s="14" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="X8" s="14" t="n">
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>22.1</v>
+        <v>86.7</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>34.2</v>
+        <v>20.2</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1194,76 +1182,72 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2656.2</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2262
-411464141
-</t>
-        </is>
+        <v>2636</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1169.7</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="10" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>44.2</v>
+        <v>1644.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="M9" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>2.8</v>
+        <v>258.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>949.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1685</v>
+        <v>1169</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="S9" s="3" t="n"/>
+        <v>71.8</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>127.7</v>
+      </c>
       <c r="T9" s="3" t="n">
-        <v>55.9</v>
+        <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>24.1</v>
+        <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>139.7</v>
+        <v>1139.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>9.6</v>
+        <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>38.9</v>
+        <v>28.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>16.2</v>
+        <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>90.2</v>
+        <v>1120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1279,72 +1263,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F10" s="12" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="13" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="13" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>28.8</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n">
-        <v>3.4</v>
+        <v>13.7</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+      <c r="L10" s="14" t="n">
+        <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>32.6</v>
+        <v>16.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="P10" s="3" t="n"/>
+        <v>236.6</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>99.8</v>
+      </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>5.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U10" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U10" s="14" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="W10" s="13" t="n">
-        <v>38.2</v>
+      <c r="V10" s="14" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="W10" s="14" t="n">
+        <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>0.8</v>
+        <v>17.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>184.1</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>11.2</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1360,75 +1346,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>422.9</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>42.1</v>
+        <v>1427.8</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.1</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>4.5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K11" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="K11" s="3" t="inlineStr"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-8
-</t>
-        </is>
-      </c>
+        <v>16.4</v>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
-        <v>12</v>
+        <v>113</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q11" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Q11" s="14" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="3" t="n"/>
+      <c r="R11" s="14" t="n">
+        <v>148.9</v>
+      </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="V11" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="U11" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="14" t="n">
         <v>21.7</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>424</v>
-      </c>
-      <c r="Z11" s="3" t="n"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1443,78 +1417,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>6.1</v>
-      </c>
+        <v>206.1</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>6.4</v>
+        <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0.2</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>31.3</v>
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6.8</v>
+        <v>16.2</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>92.2</v>
+        <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45
-76
-</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="W12" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="X12" s="14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1530,75 +1500,75 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E13" s="12" t="n">
+        <v>1601.3</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E13" s="13" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="12" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G13" s="12" t="n">
+      <c r="F13" s="13" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G13" s="13" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="n">
-        <v>11.8</v>
+      <c r="H13" s="14" t="n">
+        <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="3" t="n">
+      <c r="J13" s="14" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>11.7</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>1249</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>39.6</v>
-      </c>
-      <c r="Q13" s="3" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="Q13" s="14" t="n">
         <v>33.2</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="V13" s="13" t="n">
-        <v>87.2</v>
+        <v>3.5</v>
+      </c>
+      <c r="U13" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>28.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>15.1</v>
+      </c>
+      <c r="X13" s="14" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
+        <v>7.1</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>1265.4</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1613,22 +1583,22 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E14" s="12" t="n">
+        <v>1488</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G14" s="12" t="n">
+      <c r="F14" s="13" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="H14" s="3" t="n">
-        <v>11.4</v>
+      <c r="H14" s="14" t="n">
+        <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>8.1</v>
@@ -1637,51 +1607,45 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="P14" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="P14" s="14" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="14" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S14" s="3" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
       <c r="T14" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>4.4</v>
+        <v>161.1</v>
+      </c>
+      <c r="U14" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="14" t="n">
+        <v>14.4</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
+        <v>20.8</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>431.2</v>
+      </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>9</t>
@@ -1696,76 +1660,68 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>552.4</v>
+        <v>1832.9</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>34.3</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
+      <c r="E15" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G15" s="14" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>3.6</v>
+        <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>7.2</v>
+        <v>17.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L15" s="14" t="n">
         <v>16.5</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>2.8</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.8</v>
+        <v>92.8</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>6.9</v>
-      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="U15" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>22.1</v>
-      </c>
+        <v>115.4</v>
+      </c>
+      <c r="U15" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="V15" s="3" t="inlineStr"/>
       <c r="W15" s="3" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>23.4</v>
+        <v>123.4</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1781,88 +1737,74 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2577.7</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>82.8</v>
+        <v>0.9</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1291.6</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>2726.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>18.3</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.2</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>35.3</v>
+        <v>97.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1811
-14
-</t>
-        </is>
+        <v>56.2</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>822.3</v>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">443222
-181909191
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>189.9</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>2952.9</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>2121.5</v>
+        <v>2212</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>54.7</v>
+        <v>1154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23.6</v>
+        <v>1083.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>820.6</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-7918949
-</t>
-        </is>
+        <v>182</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>1188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>1131</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>48.3</v>
+        <v>148.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>148.8</v>
+        <v>11245.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>19.1</v>
+        <v>1124.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1878,75 +1820,71 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>2.6</v>
+        <v>315.4</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>6.8</v>
+        <v>16</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>1.7</v>
-      </c>
+        <v>7.1</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N17" s="3" t="n"/>
+        <v>4.2</v>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="P17" s="13" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="Q17" s="13" t="n">
-        <v>60.9</v>
+        <v>942.5</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>72.3</v>
+        <v>4.7</v>
+      </c>
+      <c r="S17" s="14" t="n">
+        <v>87.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>18.2</v>
+        <v>37.6</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>4.8</v>
+        <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>0.7</v>
+        <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>212.1</v>
-      </c>
-      <c r="Z17" s="3" t="n">
-        <v>44.9</v>
-      </c>
+        <v>229.2</v>
+      </c>
+      <c r="Z17" s="3" t="inlineStr"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1960,77 +1898,73 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
-2
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="3" t="n">
-        <v>2.5</v>
+      <c r="C18" s="3" t="n">
+        <v>532.1</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>12.4</v>
+        <v>16.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="14" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N18" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>7.6</v>
+      </c>
+      <c r="N18" s="3" t="inlineStr"/>
       <c r="O18" s="3" t="n">
-        <v>7.5</v>
+        <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>5.9</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q18" s="14" t="n">
+        <v>911.1</v>
+      </c>
+      <c r="R18" s="14" t="n">
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>166.9</v>
-      </c>
-      <c r="U18" s="13" t="n">
-        <v>72.59999999999999</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W18" s="3" t="n">
-        <v>14.4</v>
+        <v>115.5</v>
+      </c>
+      <c r="U18" s="14" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="14" t="n">
+        <v>184.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>0.2</v>
+        <v>29.7</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2045,49 +1979,43 @@
           <t>12</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-2975
-</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F19" s="3" t="n">
+      <c r="C19" s="3" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F19" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="13" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>12.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="14" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L19" s="14" t="n">
         <v>13.5</v>
       </c>
-      <c r="M19" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N19" s="3" t="n"/>
+      <c r="M19" s="3" t="inlineStr"/>
+      <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="n">
-        <v>60.8</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
@@ -2096,27 +2024,27 @@
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>6.1</v>
+        <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>96.2</v>
-      </c>
+        <v>112.8</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="V19" s="3" t="inlineStr"/>
       <c r="W19" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.1</v>
+        <v>0.1</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z19" s="3" t="n"/>
+        <v>122</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>29.7</v>
+      </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>12</t>
@@ -2130,56 +2058,51 @@
           <t>13</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">446466240
-212
-79719019
-</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>12.3</v>
+      <c r="C20" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D20" s="15" t="inlineStr"/>
+      <c r="E20" s="14" t="n">
+        <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="14" t="n">
         <v>14.1</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.5</v>
+        <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L20" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L20" s="14" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
+      </c>
+      <c r="N20" s="14" t="n">
+        <v>11.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5</v>
+        <v>522</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
-        <v>10.6</v>
+      <c r="R20" s="14" t="n">
+        <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
@@ -2188,21 +2111,23 @@
         <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V20" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>12.4</v>
+        <v>29.8</v>
+      </c>
+      <c r="V20" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <v>182.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>2.7</v>
+        <v>0.1</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+        <v>52</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>28.7</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -2219,43 +2144,41 @@
       <c r="C21" s="3" t="n">
         <v>542.2</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G21" s="12" t="n">
+      <c r="D21" s="3" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G21" s="14" t="n">
         <v>14.5</v>
       </c>
-      <c r="H21" s="13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>1.6</v>
+      <c r="H21" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="14" t="n">
+        <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>11.9</v>
+        <v>10</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="N21" s="14" t="n">
+        <v>10.5</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="P21" s="3" t="n">
+      <c r="P21" s="14" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2265,28 +2188,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1.6</v>
+        <v>17.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>12.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="V21" s="3" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V21" s="14" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="14" t="n">
         <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>2.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2302,75 +2225,75 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F22" s="11" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>1536.3</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="14" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="3" t="n">
-        <v>13.3</v>
+      <c r="H22" s="14" t="n">
+        <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2.6</v>
+        <v>7.6</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L22" s="3" t="n">
+      <c r="K22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="14" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="M22" s="14" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="N22" s="3" t="inlineStr"/>
       <c r="O22" s="3" t="n">
-        <v>21.1</v>
+        <v>51</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>6.8</v>
+        <v>16.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="V22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="V22" s="14" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>2.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="Z22" s="3" t="n"/>
+        <v>216.3</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>126.2</v>
+      </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>15</t>
@@ -2384,79 +2307,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="10" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>17.1</v>
+      <c r="C23" s="3" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>1117.1</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44255
-82947
-</t>
-        </is>
+      <c r="H23" s="3" t="n">
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.2</v>
+        <v>719.1</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>1.1</v>
+        <v>20.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>23</v>
+        <v>1212</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>2.4</v>
+        <v>141.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>5.4</v>
+        <v>154.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.59999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="S23" s="3" t="n">
         <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>4.9</v>
+        <v>182.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>292</v>
+        <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>30.5</v>
+        <v>1302.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>68.8</v>
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>17.3</v>
+        <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>192.1</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2472,76 +2393,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>5026.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="D24" s="13" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>14.1</v>
+      <c r="E24" s="13" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>23.4</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>78.40000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>2</v>
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="J24" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J24" s="14" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="n">
-        <v>3.3</v>
-      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>10.1</v>
+      </c>
+      <c r="N24" s="3" t="inlineStr"/>
       <c r="O24" s="3" t="n">
-        <v>54.6</v>
+        <v>4.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="14" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="U24" s="13" t="n">
-        <v>87.2</v>
+        <v>116.6</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>37.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="W24" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>2.5</v>
+        <v>25.5</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2557,79 +2474,73 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>12.2</v>
+        <v>425.5</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L25" s="14" t="n">
         <v>19.8</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>11.8</v>
+      </c>
+      <c r="N25" s="3" t="inlineStr"/>
       <c r="O25" s="3" t="n">
-        <v>400.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>14</v>
+        <v>140</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>114</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="T25" s="3" t="n"/>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-2
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-171111
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>1</v>
+        <v>911.1</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="V25" s="14" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="14" t="n">
+        <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
+        <v>1457.5</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>1112.1</v>
+      </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -2646,73 +2557,71 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G26" s="3" t="n">
+      <c r="D26" s="13" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G26" s="13" t="n">
         <v>15.5</v>
       </c>
-      <c r="H26" s="3" t="n">
-        <v>15</v>
+      <c r="H26" s="14" t="n">
+        <v>11.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>72.3</v>
+        <v>3.3</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K26" s="13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="L26" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L26" s="14" t="n">
         <v>15.9</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="N26" s="3" t="inlineStr"/>
       <c r="O26" s="3" t="n">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>20.2</v>
+        <v>18</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V26" s="13" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="W26" s="13" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="X26" s="3" t="n">
-        <v>0.9</v>
-      </c>
+        <v>33.4</v>
+      </c>
+      <c r="V26" s="14" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
+        <v>227</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>125</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2727,80 +2636,68 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>28.58</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>6.6</v>
+        <v>550.1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
+        <v>12.4</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="L27" s="14" t="n">
         <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N27" s="3" t="n">
-        <v>98.5</v>
-      </c>
+        <v>10.8</v>
+      </c>
+      <c r="N27" s="3" t="inlineStr"/>
       <c r="O27" s="3" t="n">
-        <v>528</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>2.2</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>29.3</v>
+        <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S27" s="3" t="n">
-        <v>7.1</v>
-      </c>
+        <v>18.5</v>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
       <c r="T27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>3.4</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="14" t="n">
+        <v>37.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>22.2</v>
+        <v>28.2</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X27" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="X27" s="3" t="inlineStr"/>
+      <c r="Y27" s="3" t="n">
+        <v>1026.6</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="Y27" s="3" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2816,80 +2713,76 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>621</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="G28" s="3" t="n">
+        <v>1621</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G28" s="13" t="n">
         <v>18.6</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>14.4</v>
+        <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>28.1</v>
+        <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>20</v>
+        <v>10.8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>1.8</v>
+      <c r="M28" s="14" t="n">
+        <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>2.8</v>
+        <v>18.5</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>428</v>
-      </c>
-      <c r="P28" s="3" t="n">
-        <v>18.8</v>
+        <v>1428</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>120.8</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>30.8</v>
+        <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>13.4</v>
+        <v>0.3</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>166</v>
+        <v>29.4</v>
       </c>
       <c r="U28" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="V28" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="W28" s="3" t="n">
+      <c r="V28" s="14" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="W28" s="14" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>0.8</v>
+        <v>16.9</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="Z28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-309
-</t>
-        </is>
+        <v>18.6</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>30.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2905,75 +2798,75 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G29" s="3" t="n">
+        <v>624.9</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G29" s="13" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>20.4</v>
+        <v>17.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>6</v>
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>0.8</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.3</v>
+        <v>141.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q29" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R29" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="Q29" s="14" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="R29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>4.6</v>
+        <v>45.6</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="14" t="n">
         <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>6.9</v>
+        <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n">
+        <v>3068.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2988,75 +2881,71 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>8.1</v>
+        <v>2781.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>18.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>2.5</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>32</v>
+        <v>372</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>55.8</v>
+        <v>155.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0</v>
+        <v>110.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>6.3</v>
+        <v>130.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>232.3</v>
+        <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>51.2</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>33.5</v>
+        <v>153.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.4</v>
-      </c>
+        <v>70.90000000000001</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>9</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>194.1</v>
+        <v>8194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>6.8</v>
+        <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="Y30" s="3" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3071,71 +2960,65 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>556.4</v>
-      </c>
-      <c r="D31" s="10" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="D31" s="13" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>0.4</v>
+      <c r="E31" s="13" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>5</v>
+        <v>11.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J31" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J31" s="14" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="13" t="n">
-        <v>92.90000000000001</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N31" s="3" t="n">
-        <v>43.1</v>
-      </c>
+      <c r="M31" s="3" t="inlineStr"/>
+      <c r="N31" s="3" t="inlineStr"/>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>1.3</v>
+        <v>10.3</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="R31" s="13" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T31" s="3" t="n"/>
+        <v>31</v>
+      </c>
+      <c r="R31" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="n">
+        <v>114.5</v>
+      </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="W31" s="3" t="n">
+      <c r="V31" s="14" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="W31" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>8.4</v>
+        <v>18.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>2.5</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3153,70 +3036,68 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>13.2</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>10</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>0.8</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="N32" s="3" t="inlineStr"/>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="S32" s="3" t="n">
-        <v>4.7</v>
-      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
       <c r="T32" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>424.1</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="W32" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="14" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="W32" s="14" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+        <v>17.1</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="n">
+        <v>31.9</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -3230,74 +3111,72 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="11" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G33" s="3" t="n">
+      <c r="C33" s="3" t="n">
+        <v>448.7</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G33" s="14" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>7.1</v>
+        <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>35.8</v>
+        <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L33" s="14" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>5.7</v>
+      <c r="M33" s="14" t="n">
+        <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q33" s="3" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="R33" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="P33" s="14" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="13" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="S33" s="3" t="inlineStr"/>
       <c r="T33" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W33" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="X33" s="3" t="n">
-        <v>1.1</v>
+        <v>30.3</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="14" t="n">
+        <v>218</v>
+      </c>
+      <c r="W33" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="14" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>10.2</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -3314,78 +3193,70 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="D34" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr"/>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>21.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>6</v>
+        <v>14.2</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N34" s="3" t="n">
-        <v>0.8</v>
+      <c r="M34" s="14" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N34" s="14" t="n">
+        <v>116</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>52.2</v>
+        <v>12952.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="R34" s="14" t="n">
         <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>2.1</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>30.3</v>
+        <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="V34" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V34" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="14" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+      <c r="X34" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-178
-</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>11.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3403,62 +3274,60 @@
       <c r="C35" s="3" t="n">
         <v>433.9</v>
       </c>
-      <c r="D35" s="11" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>12.4</v>
+      <c r="D35" s="13" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H35" s="14" t="n">
+        <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>14.2</v>
+        <v>5.3</v>
+      </c>
+      <c r="K35" s="14" t="n">
+        <v>28.5</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N35" s="3" t="n">
-        <v>10.3</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="N35" s="3" t="inlineStr"/>
       <c r="O35" s="3" t="n">
-        <v>2.1</v>
+        <v>124</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>2.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+        <v>30.3</v>
+      </c>
+      <c r="R35" s="14" t="n">
+        <v>15.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>55</v>
+        <v>222.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="V35" s="3" t="n">
-        <v>22.5</v>
+        <v>23.9</v>
+      </c>
+      <c r="V35" s="14" t="n">
+        <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
@@ -3467,9 +3336,11 @@
         <v>9.699999999999999</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+        <v>1839.8</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>422.1</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3484,73 +3355,73 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>13.3</v>
+        <v>341.3</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>14.3</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>4</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="3" t="n">
-        <v>9.1</v>
+        <v>21.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L36" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L36" s="14" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N36" s="3" t="n"/>
+      <c r="M36" s="14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="N36" s="3" t="inlineStr"/>
       <c r="O36" s="3" t="n">
-        <v>11</v>
+        <v>194</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>29.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="R36" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="R36" s="14" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>22.8</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>21.6</v>
+        <v>0.1</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="W36" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W36" s="14" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>1.6</v>
+      <c r="X36" s="14" t="n">
+        <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+        <v>218.8</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>116.8</v>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -3564,71 +3435,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n"/>
-      <c r="D37" s="10" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>18.5</v>
+      <c r="C37" s="3" t="n">
+        <v>966.1</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>1181.6</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>168.9</v>
+      </c>
+      <c r="F37" s="9" t="n">
+        <v>1110.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.2</v>
+        <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>42.4</v>
+        <v>35.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>101</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>36.4</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>821.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="N37" s="3" t="n"/>
+        <v>123.2</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>4.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>20.2</v>
+        <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>59.8</v>
+        <v>594.1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>24.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>0.2</v>
+        <v>1782.6</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>4.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>34.1</v>
+        <v>1141</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>3.4</v>
+        <v>1134.2</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>79</v>
+        <v>0.6</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>49.2</v>
+        <v>949.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>183.1</v>
+        <v>181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>96.2</v>
+        <v>92</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3644,73 +3521,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="D38" s="11" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="E38" s="11" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="F38" s="10" t="n">
-        <v>16.3</v>
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>22.4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>82.7</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>5.8</v>
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <v>111.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>36.1</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>53.2</v>
-      </c>
-      <c r="N38" s="3" t="n">
-        <v>47.8</v>
-      </c>
+        <v>10.6</v>
+      </c>
+      <c r="N38" s="3" t="inlineStr"/>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>1418</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>59.8</v>
-      </c>
-      <c r="Q38" s="13" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="R38" s="13" t="n">
-        <v>48.5</v>
+        <v>16.9</v>
+      </c>
+      <c r="Q38" s="14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="R38" s="14" t="n">
+        <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>9.5</v>
+        <v>940.1</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>28.9</v>
+        <v>30.8</v>
+      </c>
+      <c r="U38" s="14" t="n">
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>2.8</v>
+        <v>22.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>0.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>2.4</v>
+        <v>37.4</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>18.4</v>
@@ -3729,47 +3602,45 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5444.4</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>6.5</v>
+        <v>314.6</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="14" t="n">
+        <v>80</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>1.2</v>
+        <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>51.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M39" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L39" s="14" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="M39" s="14" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N39" s="3" t="inlineStr"/>
       <c r="O39" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="P39" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="P39" s="3" t="inlineStr"/>
       <c r="Q39" s="3" t="n">
-        <v>26.7</v>
+        <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>15.5</v>
@@ -3778,25 +3649,23 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W39" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="X39" s="3" t="n">
+        <v>122.4</v>
+      </c>
+      <c r="U39" s="14" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="V39" s="3" t="inlineStr"/>
+      <c r="W39" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="X39" s="14" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>36.4</v>
+        <v>396.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>22.2</v>
+        <v>226.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3812,74 +3681,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>51.2</v>
+        <v>617.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="G40" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="H40" s="14" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="I40" s="14" t="n">
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>2.2</v>
+        <v>18.3</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="L40" s="14" t="n">
+        <v>16.2</v>
+      </c>
       <c r="M40" s="3" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>94.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>15.5</v>
+        <v>30</v>
+      </c>
+      <c r="R40" s="14" t="n">
+        <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="U40" s="3" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="V40" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W40" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="X40" s="3" t="n">
-        <v>1.1</v>
+        <v>19</v>
+      </c>
+      <c r="U40" s="14" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="V40" s="3" t="inlineStr"/>
+      <c r="W40" s="14" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="X40" s="14" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>21</v>
+        <v>8120.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>22.6</v>
+        <v>1221.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3895,76 +3764,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>16.8</v>
+        <v>587.5</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>1.2</v>
+        <v>15</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5.6</v>
+        <v>16.6</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>16.2</v>
+        <v>10.8</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>18</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N41" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="N41" s="3" t="inlineStr"/>
       <c r="O41" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="P41" s="3" t="n">
-        <v>18.8</v>
+        <v>49</v>
+      </c>
+      <c r="P41" s="14" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="R41" s="3" t="n">
-        <v>15</v>
+        <v>29.8</v>
+      </c>
+      <c r="R41" s="14" t="n">
+        <v>15.3</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>2.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>197.5</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>26</v>
+        <v>122.2</v>
+      </c>
+      <c r="U41" s="14" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="V41" s="14" t="n">
+        <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>14.7</v>
+        <v>15.4</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>1.1</v>
+        <v>10.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>28.9</v>
+        <v>128.8</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>16.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3979,81 +3846,75 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-4811
-</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E42" s="12" t="n">
+      <c r="C42" s="3" t="n">
+        <v>481.1</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M42" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr"/>
+      <c r="O42" s="3" t="n">
+        <v>920.9</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="R42" s="14" t="n">
         <v>14.7</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K42" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q42" s="3" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>45.5</v>
-      </c>
       <c r="S42" s="3" t="n">
-        <v>9.300000000000001</v>
+        <v>19.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>2.6</v>
+        <v>28.1</v>
+      </c>
+      <c r="U42" s="14" t="n">
+        <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
-        <v>22.5</v>
+        <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>1.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>5.8</v>
+        <v>192.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.4</v>
+        <v>10.2</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4069,74 +3930,72 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E43" s="12" t="n">
+        <v>354</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E43" s="13" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>14.2</v>
+      <c r="F43" s="13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G43" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>8.5</v>
+        <v>19.7</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>10.9</v>
-      </c>
+        <v>17.7</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr"/>
       <c r="N43" s="3" t="n">
-        <v>98.5</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" s="3" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="R43" s="14" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>9.9</v>
+        <v>18.8</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>28.7</v>
+        <v>201.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>24.6</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>19.9</v>
+        <v>22.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X43" s="13" t="n">
-        <v>41.8</v>
+        <v>13.3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>285.3</v>
+        <v>1925.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>16.5</v>
+        <v>246.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4152,76 +4011,72 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>17.7</v>
+        <v>238</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="14" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="J44" s="14" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="14" t="n">
+        <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>16.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>581.5</v>
+        <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="R44" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="S44" s="13" t="n">
-        <v>89.8</v>
+        <v>16.6</v>
+      </c>
+      <c r="Q44" s="14" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="R44" s="14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>21.8</v>
+        <v>109.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>1.4</v>
+        <v>32.8</v>
       </c>
       <c r="V44" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>8.4</v>
+        <v>21.2</v>
+      </c>
+      <c r="W44" s="14" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X44" s="14" t="n">
+        <v>12.2</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>24.6</v>
+        <v>182.4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4237,78 +4092,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="D45" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E45" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>15.7</v>
+        <v>33102.9</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>11871.5</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>191.9</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1122.1</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>119.1</v>
+        <v>11.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>6.1</v>
+        <v>82224.60000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>90.8</v>
+        <v>1512.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>3.5</v>
+        <v>1822.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>16.6</v>
+        <v>111011.1</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
+        <v>1815.9</v>
+      </c>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>0.4</v>
+        <v>11226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>0.2</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>22.2</v>
+        <v>133.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="S45" s="3" t="n"/>
+        <v>1021.8</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>183.8</v>
+      </c>
       <c r="T45" s="3" t="n">
-        <v>2.2</v>
+        <v>1836.9</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>52.8</v>
+        <v>8888.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21.2</v>
+        <v>21462.1</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>14.7</v>
+        <v>106.1</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.2</v>
+        <v>1098.7</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-11
-</t>
-        </is>
+        <v>1222.8</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>1117.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4324,68 +4175,68 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>232.2</v>
-      </c>
-      <c r="D46" s="11" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="E46" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H46" s="14" t="n">
+        <v>12.1</v>
+      </c>
       <c r="I46" s="3" t="n">
-        <v>35</v>
+        <v>6.8</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>524.2</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
+        <v>8.6</v>
+      </c>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="14" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M46" s="14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N46" s="3" t="inlineStr"/>
       <c r="O46" s="3" t="n">
-        <v>26.5</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="Q46" s="13" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="R46" s="13" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="Q46" s="14" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>9</v>
+      </c>
       <c r="T46" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U46" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="V46" s="3" t="n">
-        <v>751.9</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U46" s="14" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="X46" s="3" t="n">
-        <v>64.8</v>
-      </c>
       <c r="Y46" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,26 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,28 +146,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,49 +775,55 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1569.8</v>
-      </c>
-      <c r="D4" s="13" t="n">
+        <v>562.8</v>
+      </c>
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="14" t="n">
-        <v>72.8</v>
+      <c r="H4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="J4" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="M4" s="3" t="n">
         <v>4.6</v>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="14" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="R4" s="14" t="n">
+      <c r="Q4" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R4" s="8" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -854,74 +848,76 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>512.7</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E5" s="13" t="n">
+        <v>15127.1</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="13" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>21.8</v>
+      <c r="F5" s="12" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>28.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2.4</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>44.2</v>
+        <v>8.4</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="M5" s="14" t="n">
-        <v>65.5</v>
+        <v>8</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="14" t="n">
-        <v>14</v>
+      <c r="R5" s="8" t="n">
+        <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
-      <c r="T5" s="3" t="inlineStr"/>
-      <c r="U5" s="14" t="n">
+      <c r="T5" s="3" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="U5" s="3" t="n">
         <v>46.8</v>
       </c>
-      <c r="V5" s="14" t="n">
+      <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="W5" s="14" t="n">
-        <v>10.3</v>
+      <c r="W5" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>32.2</v>
+        <v>38.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -937,19 +933,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1504.8</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>2062.3</v>
+        <v>2304.8</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
@@ -961,25 +957,27 @@
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="N6" s="14" t="n">
-        <v>89.8</v>
+        <v>6</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>1140</v>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="14" t="n">
+        <v>2109.8</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q6" s="3" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="14" t="n">
+      <c r="R6" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -989,22 +987,22 @@
         <v>12.2</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>1</v>
+        <v>41.8</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>14.2</v>
+      <c r="W6" s="8" t="n">
+        <v>64.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>201.2</v>
+        <v>20.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>230.2</v>
+        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1022,72 +1020,74 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <v>10.9</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="8" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="K7" s="14" t="n">
-        <v>8</v>
+        <v>16.9</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>5.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>22.1</v>
+        <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="R7" s="14" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>8.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U7" s="14" t="n">
-        <v>42.4</v>
+        <v>6.8</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W7" s="14" t="n">
-        <v>13.5</v>
+        <v>29.1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>13.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>116.3</v>
+        <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>33.4</v>
+        <v>23.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1103,37 +1103,41 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>485.1</v>
+        <v>11285.1</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
+        <v>24.4</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>91</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.2</v>
+        <v>81.2</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>110.8</v>
+        <v>19.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>236.5</v>
+        <v>36</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1141,33 +1145,31 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="S8" s="14" t="n">
-        <v>71</v>
+      <c r="S8" s="3" t="n">
+        <v>87</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U8" s="14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="W8" s="14" t="n">
+      <c r="V8" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W8" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="X8" s="14" t="n">
-        <v>11.7</v>
+      <c r="X8" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="Z8" s="3" t="n">
-        <v>20.2</v>
-      </c>
+        <v>11098.2</v>
+      </c>
+      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1182,51 +1184,55 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2636</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>1169.7</v>
-      </c>
-      <c r="E9" s="9" t="n">
+        <v>2666</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>23.3</v>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="10" t="n">
+      <c r="F9" s="10" t="n">
+        <v>1413.4</v>
+      </c>
+      <c r="G9" s="13" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>39.1</v>
+        <v>329.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1644.2</v>
+        <v>614.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>67.09999999999999</v>
+      </c>
       <c r="M9" s="3" t="n">
-        <v>0.2</v>
+        <v>32.9</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>258.7</v>
+        <v>121.7</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>1183</v>
+        <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>949.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1169</v>
+        <v>169</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>127.7</v>
+        <v>27.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
@@ -1235,7 +1241,7 @@
         <v>1224.1</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>1139.7</v>
+        <v>139.7</v>
       </c>
       <c r="W9" s="3" t="n">
         <v>169.6</v>
@@ -1247,7 +1253,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1120.2</v>
+        <v>1158.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1265,72 +1271,70 @@
       <c r="C10" s="3" t="n">
         <v>231.2</v>
       </c>
-      <c r="D10" s="13" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F10" s="13" t="n">
+      <c r="D10" s="10" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F10" s="10" t="n">
         <v>22.3</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>28.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="N10" s="3" t="n">
-        <v>1.5</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="n">
-        <v>236.6</v>
+        <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>99.8</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.4</v>
+        <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="U10" s="14" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V10" s="14" t="n">
+      <c r="U10" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="14" t="n">
+      <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="3" t="n">
-        <v>17.8</v>
+      <c r="X10" s="8" t="n">
+        <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>99.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1346,33 +1350,37 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1427.8</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="E11" s="15" t="inlineStr"/>
-      <c r="F11" s="3" t="n">
-        <v>23.9</v>
+        <v>427.9</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>33.8</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0.6</v>
+        <v>13.9</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>11.7</v>
+      </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>16.4</v>
+        <v>61.4</v>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="n">
@@ -1381,24 +1389,22 @@
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="14" t="n">
-        <v>148.9</v>
+      <c r="R11" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="U11" s="14" t="n">
-        <v>31</v>
-      </c>
-      <c r="V11" s="14" t="n">
-        <v>21.7</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
@@ -1417,29 +1423,31 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>206.1</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="G12" s="14" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G12" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
+      <c r="I12" s="3" t="n">
+        <v>6.1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>19.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>18.5</v>
@@ -1448,22 +1456,22 @@
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q12" s="14" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R12" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16.2</v>
+        <v>6</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
@@ -1472,19 +1480,19 @@
         <v>89.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="W12" s="14" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W12" s="8" t="n">
         <v>84</v>
       </c>
-      <c r="X12" s="14" t="n">
-        <v>2.3</v>
+      <c r="X12" s="8" t="n">
+        <v>12.9</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>47</v>
+        <v>1217</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>4.8</v>
+        <v>1835.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1500,31 +1508,31 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1601.3</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>34.4</v>
+        <v>601.3</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>34.3</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H13" s="14" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H13" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>16.6</v>
@@ -1534,40 +1542,40 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>1249</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q13" s="14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="3" t="n">
-        <v>13.8</v>
+      <c r="R13" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U13" s="14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>44</v>
       </c>
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>15.1</v>
       </c>
-      <c r="X13" s="14" t="n">
-        <v>10.2</v>
+      <c r="X13" s="8" t="n">
+        <v>2.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>1265.4</v>
+        <v>86.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1583,21 +1591,21 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1488</v>
-      </c>
-      <c r="D14" s="13" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E14" s="13" t="n">
+        <v>489</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="13" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H14" s="14" t="n">
+      <c r="F14" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>13.6</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1612,39 +1620,47 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="N14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O14" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="P14" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>7.3</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>161.1</v>
-      </c>
-      <c r="U14" s="14" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U14" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="14" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+      <c r="V14" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>431.2</v>
+        <v>31.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1660,69 +1676,73 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1832.9</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>16.3</v>
+        <v>252.1</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>16.8</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="n">
+        <v>0.9</v>
+      </c>
       <c r="O15" s="3" t="n">
-        <v>98</v>
+        <v>4.8</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>92.8</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="R15" s="8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>11.6</v>
+      </c>
       <c r="T15" s="3" t="n">
         <v>115.4</v>
       </c>
-      <c r="U15" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="n">
+      <c r="U15" s="8" t="n">
+        <v>820.8</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W15" s="8" t="n">
         <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y15" s="3" t="n">
-        <v>123.4</v>
-      </c>
-      <c r="Z15" s="3" t="n">
-        <v>24.4</v>
-      </c>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1737,22 +1757,22 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>1291.6</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>2726.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>18.3</v>
+        <v>237.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>182391.6</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>216.8</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>161.8</v>
+        <v>61.8</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>97.3</v>
@@ -1761,15 +1781,17 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>10.7</v>
+        <v>1.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>189.9</v>
+        <v>189.8</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2952.9</v>
-      </c>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>202.8</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="O16" s="3" t="n">
         <v>2212</v>
       </c>
@@ -1777,10 +1799,10 @@
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>1154.7</v>
+        <v>154.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>1083.6</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
@@ -1789,22 +1811,22 @@
         <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>1188.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>1131</v>
+        <v>131.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>12.8</v>
+        <v>172.8</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>148.3</v>
+        <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>11245.8</v>
+        <v>1143.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1124.4</v>
+        <v>1024.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1822,19 +1844,19 @@
       <c r="C17" s="3" t="n">
         <v>315.4</v>
       </c>
-      <c r="D17" s="13" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>15.3</v>
+      <c r="D17" s="10" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>13.4</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>23.6</v>
+        <v>231.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H17" s="14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
@@ -1844,15 +1866,17 @@
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N17" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="O17" s="3" t="n">
-        <v>942.5</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1861,19 +1885,19 @@
         <v>30.9</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="S17" s="14" t="n">
-        <v>87.3</v>
+        <v>14.7</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>37.6</v>
+        <v>116.4</v>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v>81.59999999999999</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>26.3</v>
+        <v>946.5</v>
       </c>
       <c r="W17" s="3" t="n">
         <v>14.5</v>
@@ -1882,9 +1906,11 @@
         <v>19.7</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>229.2</v>
-      </c>
-      <c r="Z17" s="3" t="inlineStr"/>
+        <v>29.2</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1899,72 +1925,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>532.1</v>
-      </c>
-      <c r="D18" s="13" t="n">
-        <v>33</v>
-      </c>
-      <c r="E18" s="13" t="n">
-        <v>12.4</v>
+        <v>1032.1</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>7.4</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G18" s="13" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>20.5</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>16.4</v>
+        <v>13.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.4</v>
+        <v>4.8</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="14" t="n">
+      <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="N18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q18" s="14" t="n">
-        <v>911.1</v>
-      </c>
-      <c r="R18" s="14" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>13.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="U18" s="14" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="3" t="inlineStr"/>
-      <c r="W18" s="14" t="n">
-        <v>184.4</v>
+      <c r="V18" s="8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>18.4</v>
+        <v>0.5</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1980,18 +2010,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.4</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>33.5</v>
+        <v>596.5</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>35.4</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F19" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="3" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2000,50 +2030,56 @@
       <c r="I19" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="J19" s="14" t="n">
-        <v>92.59999999999999</v>
+      <c r="J19" s="8" t="n">
+        <v>120.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>17.1</v>
+      </c>
       <c r="O19" s="3" t="n">
-        <v>160.5</v>
+        <v>60.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>16.1</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="U19" s="14" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="V19" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>26.9</v>
+      </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>0.1</v>
+        <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
         <v>122</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2059,49 +2095,51 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr"/>
-      <c r="E20" s="14" t="n">
+        <v>9390.5</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="H20" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L20" s="14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L20" s="3" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N20" s="14" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>522</v>
+        <v>25</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="14" t="n">
+      <c r="R20" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2113,20 +2151,20 @@
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="14" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W20" s="14" t="n">
-        <v>182.4</v>
+      <c r="V20" s="8" t="n">
+        <v>620.2</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>0.1</v>
+        <v>18.7</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>52</v>
+        <v>119</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>28.7</v>
+        <v>118.2</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2142,43 +2180,45 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>542.2</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G21" s="14" t="n">
+        <v>942.2</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G21" s="12" t="n">
         <v>14.5</v>
       </c>
-      <c r="H21" s="14" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="14" t="n">
+      <c r="H21" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J21" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="14" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="M21" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M21" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="N21" s="14" t="n">
-        <v>10.5</v>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="P21" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="P21" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="Q21" s="3" t="n">
@@ -2188,28 +2228,28 @@
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>117.2</v>
+        <v>17.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="14" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="W21" s="14" t="n">
-        <v>14.5</v>
+      <c r="V21" s="8" t="n">
+        <v>86.3</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>19.6</v>
+        <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
         <v>128</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>217.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2225,21 +2265,21 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1536.3</v>
-      </c>
-      <c r="D22" s="13" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E22" s="13" t="n">
+        <v>536.3</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="G22" s="14" t="n">
+      <c r="F22" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G22" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2248,16 +2288,18 @@
       <c r="J22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="K22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="14" t="n">
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="14" t="n">
+      <c r="M22" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="N22" s="3" t="inlineStr"/>
+      <c r="N22" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
       </c>
@@ -2265,34 +2307,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>24.3</v>
+        <v>31.3</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>16.8</v>
+        <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
-      </c>
-      <c r="U22" s="14" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="U22" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="14" t="n">
+      <c r="V22" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="8" t="n">
         <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>216.3</v>
+        <v>26.3</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2308,22 +2350,22 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>160.3</v>
-      </c>
-      <c r="E23" s="9" t="n">
+        <v>2517.5</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="E23" s="10" t="n">
         <v>72.5</v>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>1117.1</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>86.8</v>
+      <c r="F23" s="10" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>18.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2335,49 +2377,49 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>719.1</v>
+        <v>1.9</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>20.3</v>
+        <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1212</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>141.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>154.4</v>
+        <v>134.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>13.5</v>
+        <v>73.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>36.6</v>
+        <v>56.6</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>182.9</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1302.6</v>
+        <v>138.8</v>
       </c>
       <c r="W23" s="3" t="n">
         <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>142.8</v>
+        <v>42.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>1127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2393,47 +2435,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>309.5</v>
+        <v>543.5</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>32.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F24" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F24" s="10" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="3" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="3" t="n">
+      <c r="H24" s="8" t="n">
         <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="14" t="n">
+      <c r="J24" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="K24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
         <v>10.1</v>
       </c>
-      <c r="N24" s="3" t="inlineStr"/>
+      <c r="N24" s="3" t="n">
+        <v>4.6</v>
+      </c>
       <c r="O24" s="3" t="n">
-        <v>4.6</v>
+        <v>34.6</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R24" s="14" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2448,17 +2494,15 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
-        <v>13.8</v>
-      </c>
+      <c r="W24" s="3" t="inlineStr"/>
       <c r="X24" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>25.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2474,72 +2518,76 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>425.5</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>43.2</v>
-      </c>
-      <c r="F25" s="14" t="n">
+        <v>455.5</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="F25" s="12" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="14" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="H25" s="14" t="n">
+      <c r="G25" s="12" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="14" t="n">
+      <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
+      <c r="M25" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O25" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="P25" s="14" t="n">
-        <v>114</v>
+        <v>40</v>
+      </c>
+      <c r="P25" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>911.1</v>
-      </c>
-      <c r="R25" s="14" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="S25" s="3" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="R25" s="8" t="n">
+        <v>148</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>87.3</v>
+      </c>
       <c r="T25" s="3" t="n">
-        <v>120.2</v>
+        <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="V25" s="14" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="W25" s="14" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1457.5</v>
+        <v>1411.4</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>21821828</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2555,53 +2603,55 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>530.4</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E26" s="13" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="F26" s="13" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="F26" s="12" t="n">
         <v>22.6</v>
       </c>
-      <c r="G26" s="13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H26" s="14" t="n">
-        <v>11.6</v>
+      <c r="G26" s="8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>3.3</v>
+        <v>7.3</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L26" s="14" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M26" s="8" t="n">
         <v>10.5</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O26" s="3" t="n">
-        <v>182</v>
+        <v>812</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>0.1</v>
+        <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>18</v>
@@ -2609,18 +2659,20 @@
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="14" t="n">
+      <c r="V26" s="3" t="n">
         <v>26.8</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>9.4</v>
+      </c>
       <c r="Y26" s="3" t="n">
-        <v>227</v>
+        <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>125</v>
+        <v>25.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2638,35 +2690,39 @@
       <c r="C27" s="3" t="n">
         <v>550.1</v>
       </c>
-      <c r="D27" s="13" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>16.6</v>
+      <c r="D27" s="12" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>26.1</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="n">
-        <v>10.6</v>
+      <c r="I27" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>1.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="L27" s="14" t="n">
-        <v>16.3</v>
+        <v>0</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>67.90000000000001</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="N27" s="3" t="inlineStr"/>
+      <c r="N27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="O27" s="3" t="n">
         <v>22</v>
       </c>
@@ -2677,27 +2733,29 @@
         <v>30.8</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="S27" s="3" t="inlineStr"/>
+        <v>14.5</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>7.1</v>
+      </c>
       <c r="T27" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="U27" s="14" t="n">
-        <v>37.4</v>
+      <c r="U27" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W27" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="X27" s="3" t="inlineStr"/>
+        <v>27.2</v>
+      </c>
+      <c r="W27" s="3" t="inlineStr"/>
+      <c r="X27" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="Y27" s="3" t="n">
-        <v>1026.6</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2.6</v>
+        <v>1865.9</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2713,21 +2771,21 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
-      </c>
-      <c r="D28" s="13" t="n">
-        <v>33.2</v>
+        <v>631</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>35.2</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="F28" s="13" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="F28" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="13" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="H28" s="3" t="n">
+      <c r="G28" s="8" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="H28" s="8" t="n">
         <v>0.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2737,42 +2795,42 @@
         <v>12.6</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>10.8</v>
+        <v>8</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="14" t="n">
+      <c r="M28" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>18.5</v>
+        <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1428</v>
-      </c>
-      <c r="P28" s="14" t="n">
-        <v>120.8</v>
+        <v>142</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>101</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.3</v>
+        <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="U28" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V28" s="14" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="V28" s="8" t="n">
         <v>27.7</v>
       </c>
-      <c r="W28" s="14" t="n">
+      <c r="W28" s="8" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2782,7 +2840,7 @@
         <v>18.6</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>30.8</v>
+        <v>90.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2798,62 +2856,64 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.9</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G29" s="13" t="n">
+        <v>624.8</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="E29" s="12" t="n">
         <v>22.2</v>
       </c>
+      <c r="F29" s="12" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="H29" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>18.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="K29" s="14" t="n">
-        <v>0.8</v>
+        <v>49.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>10</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.3</v>
+        <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.8</v>
+        <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>141.3</v>
+        <v>4.1</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="Q29" s="14" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="R29" s="14" t="n">
+      <c r="Q29" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R29" s="8" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>45.6</v>
+        <v>4.6</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="14" t="n">
-        <v>27.7</v>
+      <c r="U29" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v>75.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
@@ -2862,10 +2922,10 @@
         <v>16.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>18.6</v>
+        <v>118.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>3068.2</v>
+        <v>10.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2881,40 +2941,40 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2781.9</v>
-      </c>
-      <c r="D30" s="9" t="n">
+        <v>2181.9</v>
+      </c>
+      <c r="D30" s="10" t="n">
         <v>161.6</v>
       </c>
-      <c r="E30" s="9" t="n">
-        <v>714.5</v>
-      </c>
-      <c r="F30" s="9" t="n">
+      <c r="E30" s="10" t="n">
+        <v>726.5</v>
+      </c>
+      <c r="F30" s="10" t="n">
         <v>118</v>
       </c>
-      <c r="G30" s="10" t="n">
-        <v>18.7</v>
+      <c r="G30" s="13" t="n">
+        <v>18.1</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>157</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>372</v>
+        <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>155.8</v>
+        <v>139.8</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>110.9</v>
+        <v>118.9</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>82.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>130.6</v>
+        <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>222.3</v>
@@ -2923,17 +2983,19 @@
         <v>1.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>153.1</v>
+        <v>159.1</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>70.90000000000001</v>
       </c>
-      <c r="S30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="n">
+        <v>31.8</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>8194.1</v>
+        <v>1194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -2942,10 +3004,14 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+        <v>1190</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>42.9</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2960,19 +3026,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="13" t="n">
+        <v>856.4</v>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="12" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="13" t="n">
-        <v>17.4</v>
+      <c r="G31" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -2980,15 +3046,21 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="14" t="n">
+      <c r="J31" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+      <c r="M31" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
@@ -2998,27 +3070,29 @@
       <c r="Q31" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="14" t="n">
+      <c r="R31" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="S31" s="3" t="inlineStr"/>
+      <c r="S31" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T31" s="3" t="n">
-        <v>114.5</v>
+        <v>14.5</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="14" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W31" s="14" t="n">
+      <c r="V31" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="W31" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>127.3</v>
+        <v>0.2</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3037,66 +3111,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="D32" s="13" t="n">
+        <v>6144.4</v>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="12" t="n">
         <v>10.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="10" t="n">
-        <v>123.2</v>
+      <c r="G32" s="3" t="n">
+        <v>28.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.6</v>
+        <v>62.1</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.2</v>
+        <v>94.2</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>126</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N32" s="3" t="inlineStr"/>
+        <v>5.7</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="R32" s="8" t="n">
         <v>14.1</v>
       </c>
-      <c r="S32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="n">
+        <v>14.7</v>
+      </c>
       <c r="T32" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="14" t="n">
+      <c r="U32" s="3" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="V32" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W32" s="14" t="n">
+      <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Y32" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>31.9</v>
+        <v>34.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3112,18 +3196,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>448.7</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G33" s="14" t="n">
+        <v>613.7</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3136,46 +3220,50 @@
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="L33" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>8.5</v>
+        <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="P33" s="14" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="14" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="R33" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="S33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="T33" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="U33" s="3" t="inlineStr"/>
-      <c r="V33" s="14" t="n">
-        <v>218</v>
-      </c>
-      <c r="W33" s="14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="X33" s="14" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="X33" s="8" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>10.2</v>
+        <v>1455.4</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>1.3</v>
+        <v>103.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3191,21 +3279,25 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>386.6</v>
-      </c>
-      <c r="D34" s="13" t="n">
+        <v>3846.3</v>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="I34" s="3" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3213,50 +3305,50 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="8" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="N34" s="14" t="n">
-        <v>116</v>
+      <c r="N34" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>12952.2</v>
+        <v>42.2</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="14" t="n">
-        <v>13.4</v>
+      <c r="R34" s="8" t="n">
+        <v>32.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="V34" s="14" t="n">
-        <v>19</v>
-      </c>
-      <c r="W34" s="14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="W34" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="X34" s="14" t="n">
+      <c r="X34" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>11.6</v>
+        <v>1860.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3272,31 +3364,31 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>433.9</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E35" s="13" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G35" s="13" t="n">
+      <c r="F35" s="12" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G35" s="12" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="14" t="n">
+      <c r="H35" s="8" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K35" s="14" t="n">
-        <v>28.5</v>
+        <v>5.5</v>
+      </c>
+      <c r="K35" s="8" t="n">
+        <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3304,42 +3396,44 @@
       <c r="M35" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="N35" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>19.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R35" s="14" t="n">
-        <v>15.8</v>
+      <c r="R35" s="8" t="n">
+        <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>222.8</v>
-      </c>
-      <c r="U35" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="V35" s="14" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="V35" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>13.5</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>1839.8</v>
+        <v>23</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>422.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3357,70 +3451,74 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="13" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>14.3</v>
+      <c r="E36" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="J36" s="3" t="n">
-        <v>21.1</v>
+        <v>2.1</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L36" s="14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="M36" s="14" t="n">
+      <c r="M36" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
+      <c r="N36" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="O36" s="3" t="n">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>2.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="R36" s="14" t="n">
+      <c r="R36" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>34.8</v>
+        <v>32.4</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V36" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W36" s="14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v>822.1</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="14" t="n">
+      <c r="X36" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>218.8</v>
+        <v>1498.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3436,76 +3534,76 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>966.1</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>1181.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
+        <v>2216.6</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="E37" s="10" t="n">
         <v>168.9</v>
       </c>
-      <c r="F37" s="9" t="n">
-        <v>1110.2</v>
+      <c r="F37" s="10" t="n">
+        <v>11025.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>35.8</v>
+        <v>15.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>101</v>
+        <v>1018</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>36.4</v>
+        <v>8.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>123.2</v>
+        <v>23.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.1</v>
+        <v>1.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>594.1</v>
+        <v>593.5</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.5</v>
+        <v>133.6</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>1782.6</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>147.8</v>
+        <v>47.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1141</v>
+        <v>151.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>1134.2</v>
+        <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>114.1</v>
+        <v>111.3</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>0.6</v>
+        <v>87</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>949.8</v>
+        <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>181.2</v>
+        <v>1315</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3521,57 +3619,61 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>443.3</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="H38" s="14" t="n">
-        <v>111.2</v>
+        <v>473.3</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>19.2</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M38" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>10.6</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>1418</v>
+        <v>18</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="14" t="n">
+      <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>940.1</v>
+        <v>12.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="U38" s="14" t="n">
-        <v>26.9</v>
+        <v>20.3</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3602,48 +3704,52 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>314.6</v>
+        <v>914.6</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>29.2</v>
+        <v>19.21</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>14.2</v>
+        <v>141.26</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G39" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="H39" s="3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>51.2</v>
+        <v>0.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L39" s="14" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>110.2</v>
-      </c>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>510.1</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>9.6</v>
+      </c>
       <c r="O39" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R39" s="3" t="n">
-        <v>15.5</v>
+        <v>211</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="R39" s="8" t="n">
+        <v>59.3</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
@@ -3651,21 +3757,23 @@
       <c r="T39" s="3" t="n">
         <v>122.4</v>
       </c>
-      <c r="U39" s="14" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="V39" s="3" t="inlineStr"/>
-      <c r="W39" s="14" t="n">
+      <c r="U39" s="3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>396.4</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>226.6</v>
+        <v>28.8</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3681,40 +3789,40 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>617.1</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="G40" s="14" t="n">
+        <v>6471.6</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="I40" s="14" t="n">
-        <v>8.6</v>
+      <c r="I40" s="3" t="n">
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>18.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L40" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="L40" s="8" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3725,30 +3833,32 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="14" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U40" s="14" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="U40" s="8" t="n">
         <v>94.2</v>
       </c>
-      <c r="V40" s="3" t="inlineStr"/>
-      <c r="W40" s="14" t="n">
+      <c r="V40" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="W40" s="8" t="n">
         <v>84.7</v>
       </c>
-      <c r="X40" s="14" t="n">
-        <v>10.1</v>
+      <c r="X40" s="8" t="n">
+        <v>16.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>8120.6</v>
+        <v>38</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1221.6</v>
+        <v>2216.3</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3766,17 +3876,17 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="13" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E41" s="13" t="n">
+      <c r="D41" s="12" t="n">
+        <v>31.41</v>
+      </c>
+      <c r="E41" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="12" t="n">
         <v>23.8</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>15.2</v>
+        <v>166.2</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>15</v>
@@ -3788,51 +3898,51 @@
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="3" t="n">
+      <c r="M41" s="8" t="n">
         <v>11.9</v>
       </c>
-      <c r="N41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="n">
+        <v>10.1</v>
+      </c>
       <c r="O41" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="P41" s="14" t="n">
-        <v>10.8</v>
+      <c r="P41" s="8" t="n">
+        <v>19.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="R41" s="14" t="n">
-        <v>15.3</v>
+      <c r="R41" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="14" t="n">
-        <v>92.59999999999999</v>
-      </c>
-      <c r="V41" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>15.4</v>
       </c>
-      <c r="X41" s="3" t="n">
-        <v>10.1</v>
+      <c r="X41" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>128.8</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>8.6</v>
-      </c>
+        <v>1828.4</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3849,73 +3959,73 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="13" t="n">
-        <v>31.2</v>
+      <c r="D42" s="8" t="n">
+        <v>12.1</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G42" s="14" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="H42" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H42" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="M42" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="N42" s="3" t="inlineStr"/>
+      <c r="N42" s="3" t="n">
+        <v>9.5</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>920.9</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="R42" s="14" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>19.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="U42" s="14" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>13.6</v>
+        <v>13</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.8</v>
+        <v>11.5</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>192.8</v>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v>10.2</v>
-      </c>
+        <v>12.8</v>
+      </c>
+      <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3930,72 +4040,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>354</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E43" s="13" t="n">
+        <v>254</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E43" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="F43" s="13" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="G43" s="14" t="n">
+      <c r="F43" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G43" s="8" t="n">
         <v>4.1</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="8" t="n">
         <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>19.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="3" t="inlineStr"/>
+      <c r="M43" s="8" t="n">
+        <v>11.9</v>
+      </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="14" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="14" t="n">
+      <c r="R43" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>18.8</v>
+        <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>201.3</v>
+        <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>31.4</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>22.7</v>
+        <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1925.3</v>
+        <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>246.1</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4011,33 +4125,37 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="D44" s="13" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F44" s="13" t="n">
+        <v>228</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G44" s="12" t="n">
         <v>15.7</v>
       </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="14" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="J44" s="14" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="14" t="n">
+      <c r="H44" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>2.8</v>
+        <v>19.8</v>
       </c>
       <c r="N44" s="3" t="n">
         <v>8.800000000000001</v>
@@ -4046,37 +4164,37 @@
         <v>144</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="Q44" s="14" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="14" t="n">
+      <c r="R44" s="8" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>17.8</v>
+        <v>7.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>109.3</v>
+        <v>119.3</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>32.8</v>
+        <v>12.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="14" t="n">
+      <c r="W44" s="8" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="14" t="n">
-        <v>12.2</v>
+      <c r="X44" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="Y44" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="Z44" s="3" t="n">
-        <v>182.4</v>
+        <v>1122.1</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -4091,76 +4209,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v>33102.9</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>11871.5</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>191.9</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>1122.1</v>
+      <c r="C45" s="3" t="inlineStr"/>
+      <c r="D45" s="10" t="n">
+        <v>1555.1</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>411.9</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>1102.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>21</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>11.2</v>
+        <v>29.2</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>82224.60000000001</v>
+        <v>345</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1512.3</v>
+        <v>226.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1822.2</v>
+        <v>14.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>111011.1</v>
+        <v>1291.9</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>1815.9</v>
-      </c>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>80.09999999999999</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>11226.5</v>
+        <v>102261.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
+        <v>920.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>133.4</v>
+        <v>128.4</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>1021.8</v>
+        <v>11.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>183.8</v>
+        <v>182</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>1836.9</v>
+        <v>126.7</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>8888.6</v>
+        <v>102.6</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>21462.1</v>
+        <v>141.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>106.1</v>
+        <v>101</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1098.7</v>
+        <v>18.8</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.8</v>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v>1117.2</v>
-      </c>
+        <v>1222.4</v>
+      </c>
+      <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -4177,63 +4293,69 @@
       <c r="C46" s="3" t="n">
         <v>551.8</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E46" s="9" t="n">
+      <c r="D46" s="13" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="E46" s="10" t="n">
         <v>18.3</v>
       </c>
-      <c r="F46" s="9" t="n">
-        <v>23</v>
+      <c r="F46" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="14" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="14" t="n">
+      <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="14" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>9.9</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>149.4</v>
+        <v>119.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="14" t="n">
+      <c r="Q46" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>15.8</v>
+        <v>11</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="U46" s="14" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
+        <v>22.7</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>14.4</v>
+      </c>
       <c r="X46" s="3" t="n">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>28.1</v>
       </c>
       <c r="Z46" s="3" t="n">
         <v>119.6</v>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -41,14 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -146,22 +152,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -775,22 +787,22 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>562.8</v>
-      </c>
-      <c r="D4" s="12" t="n">
+        <v>569.8</v>
+      </c>
+      <c r="D4" s="13" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="13" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="13" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="13" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -805,10 +817,10 @@
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>34.5</v>
@@ -817,9 +829,9 @@
         <v>8.5</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R4" s="8" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -848,40 +860,40 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>15127.1</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E5" s="12" t="n">
+        <v>648.3</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E5" s="13" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>28.8</v>
+      <c r="F5" s="13" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" s="8" t="n">
-        <v>22.2</v>
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>36</v>
@@ -892,17 +904,17 @@
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="8" t="n">
+      <c r="R5" s="14" t="n">
         <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>444.9</v>
+        <v>12.2</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>46.8</v>
+        <v>16.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
@@ -914,10 +926,10 @@
         <v>16.5</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>96.8</v>
+        <v>26.8</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>38.2</v>
+        <v>32.2</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -933,43 +945,43 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2304.8</v>
-      </c>
-      <c r="D6" s="12" t="n">
+        <v>306.8</v>
+      </c>
+      <c r="D6" s="13" t="n">
         <v>33.8</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="13" t="n">
         <v>10.7</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="13" t="n">
         <v>22.4</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>23.9</v>
+      <c r="G6" s="13" t="n">
+        <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" s="14" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>18.8</v>
+        <v>2.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>2109.8</v>
+        <v>100.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>8.5</v>
@@ -981,28 +993,28 @@
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="3" t="n">
-        <v>41.8</v>
+      <c r="U6" s="14" t="n">
+        <v>91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="8" t="n">
-        <v>64.2</v>
+      <c r="W6" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="Y6" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>20.2</v>
-      </c>
-      <c r="Z6" s="3" t="n">
-        <v>30.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1020,38 +1032,38 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="13" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="13" t="n">
         <v>10.9</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="13" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="13" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>35</v>
@@ -1060,34 +1072,34 @@
         <v>9.4</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>31.7</v>
+        <v>34.7</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>13.8</v>
+        <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>83.59999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>1.7</v>
+        <v>21.7</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>13.3</v>
+        <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>6.5</v>
+        <v>86.3</v>
       </c>
       <c r="Y7" s="3" t="n">
         <v>16.3</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>23.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1103,16 +1115,16 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>11285.1</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>11</v>
+        <v>285.1</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>21</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>32.8</v>
+        <v>27.7</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>23.4</v>
@@ -1121,23 +1133,23 @@
         <v>11.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="J8" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J8" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>16.1</v>
+      <c r="K8" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M8" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="M8" s="14" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>36</v>
+        <v>3262</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
@@ -1145,11 +1157,11 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="8" t="n">
+      <c r="R8" s="14" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>14.3</v>
@@ -1157,17 +1169,17 @@
       <c r="U8" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="W8" s="8" t="n">
+      <c r="V8" s="3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>11.1</v>
+        <v>11.7</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>11098.2</v>
+        <v>10.2</v>
       </c>
       <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
@@ -1184,37 +1196,35 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2666</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>169.7</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1413.4</v>
-      </c>
-      <c r="G9" s="13" t="n">
+        <v>19656.5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1169.7</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr"/>
+      <c r="G9" s="15" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>329.1</v>
+        <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>614.2</v>
+        <v>14.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>168.4</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>67.09999999999999</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>32.9</v>
+        <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>121.7</v>
@@ -1223,7 +1233,7 @@
         <v>183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>48.7</v>
+        <v>49.7</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>169</v>
@@ -1253,7 +1263,7 @@
         <v>1186.2</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>1158.4</v>
+        <v>120.2</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1269,22 +1279,22 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>231.2</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>22.3</v>
+        <v>531.2</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>22.8</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1304,7 +1314,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>33</v>
@@ -1313,13 +1323,13 @@
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="U10" s="8" t="n">
-        <v>94.8</v>
+      <c r="U10" s="3" t="n">
+        <v>44.8</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.9</v>
@@ -1327,11 +1337,11 @@
       <c r="W10" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>99.2</v>
+        <v>21.2</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>8</v>
@@ -1352,37 +1362,39 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="3" t="n">
+      <c r="D11" s="13" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E11" s="13" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H11" s="8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>2.6</v>
+        <v>16.5</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
+        <v>6.4</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O11" s="3" t="n">
         <v>113</v>
       </c>
@@ -1392,17 +1404,17 @@
       <c r="Q11" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R11" s="8" t="n">
-        <v>14.9</v>
+      <c r="R11" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>822</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>81</v>
       </c>
       <c r="V11" s="3" t="inlineStr"/>
       <c r="W11" s="3" t="inlineStr"/>
@@ -1425,16 +1437,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="13" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="F12" s="8" t="n">
+      <c r="D12" s="15" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="14" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="3" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1461,38 +1471,38 @@
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="P12" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R12" s="8" t="n">
+      <c r="Q12" s="14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>89.2</v>
+        <v>29.2</v>
       </c>
       <c r="V12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W12" s="8" t="n">
+      <c r="W12" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="X12" s="8" t="n">
-        <v>12.9</v>
+      <c r="X12" s="14" t="n">
+        <v>62.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1217</v>
+        <v>1417</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>1835.8</v>
+        <v>18.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1510,23 +1520,21 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="13" t="n">
         <v>34.3</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="F13" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F13" s="13" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="8" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>11.4</v>
-      </c>
+      <c r="G13" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="3" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
@@ -1542,7 +1550,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>49</v>
+        <v>849</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
@@ -1550,8 +1558,8 @@
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="8" t="n">
-        <v>15</v>
+      <c r="R13" s="14" t="n">
+        <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1565,17 +1573,17 @@
       <c r="V13" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="8" t="n">
+      <c r="W13" s="3" t="n">
         <v>15.1</v>
       </c>
-      <c r="X13" s="8" t="n">
-        <v>2.1</v>
+      <c r="X13" s="3" t="n">
+        <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>86.5</v>
+        <v>3.5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1593,17 +1601,17 @@
       <c r="C14" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E14" s="12" t="n">
+      <c r="D14" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E14" s="13" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>24.4</v>
+      <c r="F14" s="13" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>13.6</v>
@@ -1615,16 +1623,16 @@
         <v>12.2</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1.9</v>
+        <v>0.2</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>49</v>
@@ -1636,10 +1644,10 @@
         <v>30.3</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>7.3</v>
+        <v>73.8</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
@@ -1653,14 +1661,14 @@
       <c r="W14" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="X14" s="8" t="n">
-        <v>81.2</v>
+      <c r="X14" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>80.8</v>
+        <v>1020.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>31.2</v>
+        <v>231.2</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1676,19 +1684,19 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>252.1</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>16.8</v>
+        <v>2652.1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>10.2</v>
@@ -1705,41 +1713,39 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="8" t="n">
+      <c r="M15" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>4.8</v>
+        <v>148.8</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>11.6</v>
+      <c r="Q15" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="14" t="n">
+        <v>0.8</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>115.4</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>820.8</v>
+        <v>15.4</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>3.1</v>
       </c>
       <c r="V15" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W15" s="8" t="n">
-        <v>14</v>
+        <v>98.09999999999999</v>
+      </c>
+      <c r="W15" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>18.4</v>
+        <v>8.4</v>
       </c>
       <c r="Y15" s="3" t="inlineStr"/>
       <c r="Z15" s="3" t="inlineStr"/>
@@ -1757,16 +1763,16 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>237.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>182391.6</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>216.8</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>118.2</v>
+        <v>257.2</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>8291.6</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>1118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
@@ -1781,25 +1787,23 @@
         <v>56.2</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>189.8</v>
-      </c>
+        <v>11.7</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="3" t="n">
-        <v>202.8</v>
+        <v>22.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212</v>
+        <v>2212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>154.7</v>
+        <v>184.7</v>
       </c>
       <c r="R16" s="3" t="n">
         <v>83.59999999999999</v>
@@ -1808,22 +1812,22 @@
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>188.2</v>
+        <v>128.2</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>131.5</v>
+        <v>131.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>172.8</v>
+        <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>1143.8</v>
+        <v>145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
         <v>1024.4</v>
@@ -1842,19 +1846,19 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>315.4</v>
-      </c>
-      <c r="D17" s="10" t="n">
+        <v>2313.4</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="E17" s="10" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>231.6</v>
+      <c r="E17" s="9" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>23.6</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>12.3</v>
+        <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
@@ -1865,18 +1869,20 @@
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="8" t="n">
+      <c r="K17" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="14" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1888,13 +1894,13 @@
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>116.4</v>
       </c>
-      <c r="U17" s="8" t="n">
-        <v>81.59999999999999</v>
+      <c r="U17" s="14" t="n">
+        <v>27.4</v>
       </c>
       <c r="V17" s="3" t="n">
         <v>946.5</v>
@@ -1909,7 +1915,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>24.9</v>
+        <v>29.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1925,28 +1931,26 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1032.1</v>
-      </c>
-      <c r="D18" s="8" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="D18" s="14" t="n">
         <v>22.9</v>
       </c>
-      <c r="E18" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="F18" s="13" t="n">
+      <c r="E18" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F18" s="15" t="n">
         <v>32.7</v>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>20.5</v>
-      </c>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.8</v>
+        <v>0.2</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
@@ -1958,7 +1962,7 @@
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>17.5</v>
@@ -1966,35 +1970,35 @@
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="8" t="n">
-        <v>80.40000000000001</v>
+      <c r="Q18" s="14" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.5</v>
+        <v>118.3</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W18" s="8" t="n">
+      <c r="V18" s="14" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W18" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2010,40 +2014,38 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.5</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>35.4</v>
+        <v>596.1</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>33.5</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F19" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F19" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="13" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <v>120.6</v>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>12.5</v>
+        <v>63.5</v>
       </c>
       <c r="M19" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>17.1</v>
+        <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>60.5</v>
@@ -2054,20 +2056,20 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="8" t="n">
+      <c r="R19" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>16.1</v>
+        <v>6.1</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="U19" s="8" t="n">
-        <v>61.4</v>
+      <c r="U19" s="3" t="n">
+        <v>41.4</v>
       </c>
       <c r="V19" s="3" t="n">
-        <v>26.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
@@ -2076,10 +2078,10 @@
         <v>6.7</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>29.2</v>
+        <v>292.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2095,13 +2097,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>9390.5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>17.2</v>
+        <v>322.8</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>4.8</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>12.3</v>
@@ -2109,29 +2111,29 @@
       <c r="G20" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>5.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L20" s="3" t="n">
+      <c r="L20" s="14" t="n">
         <v>18</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>11.1</v>
+      <c r="N20" s="14" t="n">
+        <v>19.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2146,22 +2148,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>22.5</v>
+        <v>44.8</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
-      <c r="V20" s="8" t="n">
-        <v>620.2</v>
-      </c>
-      <c r="W20" s="8" t="n">
+      <c r="V20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="W20" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>18.7</v>
+        <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>119</v>
+        <v>19</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>118.2</v>
@@ -2180,25 +2182,25 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>942.2</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G21" s="12" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G21" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>11.3</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>10.6</v>
@@ -2206,10 +2208,10 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M21" s="8" t="n">
+      <c r="L21" s="14" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="M21" s="14" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2236,20 +2238,20 @@
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="8" t="n">
+      <c r="V21" s="14" t="n">
         <v>86.3</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>217.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2265,18 +2267,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>536.3</v>
-      </c>
-      <c r="D22" s="12" t="n">
+        <v>936.3</v>
+      </c>
+      <c r="D22" s="13" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="13" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="13" t="n">
         <v>23.5</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G22" s="13" t="n">
         <v>16.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2298,7 +2300,7 @@
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>51</v>
@@ -2316,19 +2318,19 @@
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="U22" s="3" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="U22" s="14" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="W22" s="8" t="n">
-        <v>14.6</v>
+      <c r="W22" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>19.4</v>
+        <v>0.9</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2352,20 +2354,20 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="10" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>13.1</v>
+      <c r="D23" s="13" t="n">
+        <v>160.3</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>116.9</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>18.7</v>
+        <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>36.1</v>
@@ -2377,28 +2379,28 @@
         <v>3.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1.9</v>
+        <v>7.9</v>
       </c>
       <c r="M23" s="3" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>18.8</v>
+        <v>4.8</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>272</v>
+        <v>1272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.2</v>
+        <v>41.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>134.4</v>
+        <v>254.4</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>73.5</v>
+        <v>23.5</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>56.6</v>
+        <v>368.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2407,10 +2409,10 @@
         <v>187.2</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>138.8</v>
+        <v>138.6</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>168.8</v>
+        <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
         <v>42.8</v>
@@ -2419,7 +2421,7 @@
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1127.4</v>
+        <v>1122.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2435,49 +2437,47 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>543.5</v>
+        <v>503.5</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>92.09999999999999</v>
+        <v>32.1</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F24" s="10" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F24" s="13" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="3" t="n">
+      <c r="G24" s="13" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>12.2</v>
+      <c r="H24" s="14" t="n">
+        <v>2.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="J24" s="14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>10.1</v>
+        <v>18.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>34.6</v>
+        <v>24.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>30.9</v>
+        <v>20.9</v>
       </c>
       <c r="R24" s="3" t="n">
         <v>14.7</v>
@@ -2486,7 +2486,7 @@
         <v>7.3</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>116.6</v>
+        <v>16.6</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>37.4</v>
@@ -2494,15 +2494,17 @@
       <c r="V24" s="3" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="inlineStr"/>
+      <c r="W24" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>25.5</v>
+        <v>23.5</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2520,16 +2522,16 @@
       <c r="C25" s="3" t="n">
         <v>455.5</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="13" t="n">
         <v>31.9</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="13" t="n">
         <v>17.7</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="13" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2541,53 +2543,53 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="8" t="n">
+      <c r="K25" s="14" t="n">
         <v>10.9</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <v>21.8</v>
+      <c r="M25" s="14" t="n">
+        <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>12.2</v>
+        <v>0.1</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="P25" s="8" t="n">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="P25" s="14" t="n">
+        <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R25" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>87.3</v>
+        <v>29.4</v>
+      </c>
+      <c r="R25" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S25" s="14" t="n">
+        <v>37.3</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>122.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>42.8</v>
+        <v>12.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="W25" s="8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W25" s="3" t="n">
         <v>11</v>
       </c>
       <c r="X25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>1411.4</v>
+        <v>41.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>21821828</v>
+        <v>1112.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2603,21 +2605,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>230.4</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>530.4</v>
+      </c>
+      <c r="D26" s="13" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="13" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="13" t="n">
         <v>22.6</v>
       </c>
-      <c r="G26" s="8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H26" s="8" t="n">
+      <c r="G26" s="3" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H26" s="14" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2629,40 +2631,40 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="8" t="n">
+      <c r="L26" s="14" t="n">
         <v>13.9</v>
       </c>
-      <c r="M26" s="8" t="n">
+      <c r="M26" s="14" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>812</v>
+        <v>82</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="3" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>33.4</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="W26" s="3" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W26" s="14" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2672,7 +2674,7 @@
         <v>22</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>25.1</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2688,19 +2690,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>550.1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E27" s="12" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>26.1</v>
+        <v>50.1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
@@ -2708,26 +2710,26 @@
       <c r="I27" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <v>1.4</v>
+      <c r="J27" s="14" t="n">
+        <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="8" t="n">
-        <v>67.90000000000001</v>
+      <c r="L27" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>9.9</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
@@ -2739,23 +2741,25 @@
         <v>7.1</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>31.4</v>
+        <v>16</v>
+      </c>
+      <c r="U27" s="14" t="n">
+        <v>17.4</v>
       </c>
       <c r="V27" s="3" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
+        <v>28.2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="X27" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>126.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1865.9</v>
+        <v>196.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2771,22 +2775,22 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>631</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>35.2</v>
+        <v>1621</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>33.2</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="F28" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F28" s="13" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="8" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>0.4</v>
+      <c r="G28" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
@@ -2807,30 +2811,30 @@
         <v>1.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="P28" s="8" t="n">
-        <v>101</v>
+        <v>48</v>
+      </c>
+      <c r="P28" s="14" t="n">
+        <v>10</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>32.1</v>
+        <v>803.9</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2.6</v>
+        <v>4.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="V28" s="8" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="V28" s="14" t="n">
         <v>27.7</v>
       </c>
-      <c r="W28" s="8" t="n">
+      <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
@@ -2839,9 +2843,7 @@
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="n">
-        <v>90.8</v>
-      </c>
+      <c r="Z28" s="3" t="inlineStr"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2858,29 +2860,29 @@
       <c r="C29" s="3" t="n">
         <v>624.8</v>
       </c>
-      <c r="D29" s="12" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="F29" s="12" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="G29" s="3" t="n">
+      <c r="D29" s="13" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G29" s="13" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>18.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>10</v>
+        <v>49.3</v>
+      </c>
+      <c r="K29" s="14" t="n">
+        <v>181.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>13.7</v>
@@ -2892,15 +2894,15 @@
         <v>0.6</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>4.1</v>
+        <v>41.3</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="R29" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="R29" s="14" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2910,22 +2912,22 @@
         <v>19</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>75.7</v>
+        <v>47.1</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>27.7</v>
       </c>
       <c r="W29" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>118.6</v>
+        <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>10.8</v>
+        <v>23009</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2941,28 +2943,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2181.9</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>161.6</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>726.5</v>
-      </c>
-      <c r="F30" s="10" t="n">
+        <v>2281.9</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1561.6</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>714.5</v>
+      </c>
+      <c r="F30" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="G30" s="13" t="n">
-        <v>18.1</v>
+      <c r="G30" s="3" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>139.8</v>
+        <v>23.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>118.9</v>
@@ -2980,22 +2982,22 @@
         <v>222.3</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>1.7</v>
+        <v>91.7</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>159.1</v>
+        <v>155.1</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>70.90000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>12.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1194.1</v>
+        <v>194.1</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>126.7</v>
@@ -3004,13 +3006,13 @@
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>1190</v>
+        <v>110</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>13.6</v>
+        <v>106.9</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>42.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3026,19 +3028,19 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>856.4</v>
-      </c>
-      <c r="D31" s="12" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="D31" s="13" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="13" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="13" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="3" t="n">
-        <v>4.8</v>
+      <c r="G31" s="13" t="n">
+        <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>11.4</v>
@@ -3046,11 +3048,11 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="8" t="n">
+      <c r="J31" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>16.4</v>
@@ -3074,7 +3076,7 @@
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0.6</v>
+        <v>6.9</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3111,37 +3113,37 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>6144.4</v>
-      </c>
-      <c r="D32" s="12" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="D32" s="13" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="F32" s="12" t="n">
+      <c r="E32" s="13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F32" s="13" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>28.2</v>
+      <c r="G32" s="13" t="n">
+        <v>23.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>62.1</v>
+        <v>6.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>94.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>126</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>5.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1.2</v>
@@ -3150,12 +3152,12 @@
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>33.6</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3167,20 +3169,20 @@
       <c r="U32" s="3" t="n">
         <v>47.4</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="14" t="n">
         <v>28.3</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>13.7</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>17.1</v>
+        <v>7.1</v>
       </c>
       <c r="Y32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>34.9</v>
+        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3196,74 +3198,76 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>613.7</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E33" s="12" t="n">
+        <v>122.5</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E33" s="13" t="n">
         <v>14.6</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G33" s="12" t="n">
+      <c r="F33" s="13" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G33" s="13" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="8" t="n">
+      <c r="M33" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="8" t="n">
+      <c r="R33" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="U33" s="14" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="X33" s="8" t="n">
+      <c r="W33" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X33" s="14" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>1455.4</v>
+        <v>149.2</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>103.9</v>
+        <v>43.2</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3279,22 +3283,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3846.3</v>
-      </c>
-      <c r="D34" s="12" t="n">
+        <v>386.6</v>
+      </c>
+      <c r="D34" s="13" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="13" t="n">
         <v>15.6</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="F34" s="13" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>1.8</v>
+      <c r="G34" s="13" t="n">
+        <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>12.4</v>
+        <v>1.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.5</v>
@@ -3305,17 +3309,17 @@
       <c r="K34" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="L34" s="8" t="n">
+      <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>11.4</v>
+      <c r="M34" s="14" t="n">
+        <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>42.2</v>
+        <v>22.2</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3323,11 +3327,11 @@
       <c r="Q34" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="R34" s="8" t="n">
-        <v>32.4</v>
+      <c r="R34" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>25</v>
@@ -3335,20 +3339,20 @@
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="V34" s="8" t="n">
-        <v>89</v>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>11.8</v>
+        <v>18.7</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1860.6</v>
+        <v>1801.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3366,28 +3370,28 @@
       <c r="C35" s="3" t="n">
         <v>439.9</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="13" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="E35" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="13" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="13" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K35" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="3" t="n">
         <v>14.3</v>
       </c>
       <c r="L35" s="3" t="n">
@@ -3397,18 +3401,16 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>11.1</v>
+        <v>18.1</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="R35" s="8" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3417,8 +3419,8 @@
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="U35" s="8" t="n">
-        <v>11.1</v>
+      <c r="U35" s="3" t="n">
+        <v>23.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3430,11 +3432,9 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z35" s="3" t="n">
-        <v>19.2</v>
-      </c>
+        <v>2121.5</v>
+      </c>
+      <c r="Z35" s="3" t="inlineStr"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3454,27 +3454,23 @@
       <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="E36" s="13" t="n">
         <v>11.9</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="F36" s="13" t="n">
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="H36" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H36" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>10.5</v>
-      </c>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3482,10 +3478,10 @@
         <v>12.3</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
@@ -3500,25 +3496,25 @@
         <v>11.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>32.4</v>
+        <v>2.4</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="8" t="n">
-        <v>822.1</v>
-      </c>
-      <c r="W36" s="8" t="n">
+      <c r="V36" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="W36" s="14" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1498.8</v>
+        <v>1186</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>126.8</v>
+        <v>116.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3536,74 +3532,74 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>121.6</v>
-      </c>
-      <c r="E37" s="10" t="n">
+      <c r="D37" s="9" t="n">
+        <v>11810.6</v>
+      </c>
+      <c r="E37" s="9" t="n">
         <v>168.9</v>
       </c>
-      <c r="F37" s="10" t="n">
-        <v>11025.3</v>
+      <c r="F37" s="9" t="n">
+        <v>110.2</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>15.8</v>
+        <v>33.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>1018</v>
+        <v>180</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>23.2</v>
+        <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>1240.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>593.5</v>
+        <v>89.3</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.6</v>
+        <v>133.5</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>47.8</v>
+        <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>151.6</v>
+        <v>1151</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>111.3</v>
+        <v>114.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>49.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>1315</v>
+        <v>1181.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3619,22 +3615,22 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>473.3</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>442.2</v>
+      </c>
+      <c r="D38" s="13" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>13.9</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>19.2</v>
+      <c r="G38" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>18.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
@@ -3648,32 +3644,32 @@
       <c r="L38" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="8" t="n">
+      <c r="M38" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>12.2</v>
+        <v>27.4</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="Q38" s="14" t="n">
         <v>26.7</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>26.8</v>
+        <v>26.9</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>22.8</v>
@@ -3706,71 +3702,71 @@
       <c r="C39" s="3" t="n">
         <v>914.6</v>
       </c>
-      <c r="D39" s="13" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>141.26</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="H39" s="8" t="n">
+      <c r="D39" s="15" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="H39" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="8" t="n">
-        <v>510.1</v>
-      </c>
-      <c r="M39" s="8" t="n">
+      <c r="L39" s="14" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M39" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>211</v>
+        <v>21</v>
       </c>
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="8" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>59.3</v>
+      <c r="Q39" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>122.4</v>
-      </c>
-      <c r="U39" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U39" s="14" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="3" t="n">
+      <c r="X39" s="14" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>96.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>28.8</v>
@@ -3789,25 +3785,25 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>6471.6</v>
-      </c>
-      <c r="D40" s="12" t="n">
+        <v>641.4</v>
+      </c>
+      <c r="D40" s="13" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="13" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="13" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="3" t="n">
+      <c r="H40" s="14" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
@@ -3815,14 +3811,14 @@
       <c r="K40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="8" t="n">
+      <c r="L40" s="14" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>61</v>
@@ -3833,7 +3829,7 @@
       <c r="Q40" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="14" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3842,23 +3838,23 @@
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="U40" s="8" t="n">
-        <v>94.2</v>
+      <c r="U40" s="3" t="n">
+        <v>84.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="W40" s="8" t="n">
-        <v>84.7</v>
-      </c>
-      <c r="X40" s="8" t="n">
-        <v>16.1</v>
+      <c r="W40" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>2216.3</v>
+        <v>6.1</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3876,44 +3872,44 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="E41" s="12" t="n">
+      <c r="D41" s="13" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E41" s="13" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="13" t="n">
         <v>23.8</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>166.2</v>
+        <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="14" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="8" t="n">
+      <c r="M41" s="14" t="n">
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>10.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>19.8</v>
+        <v>99</v>
+      </c>
+      <c r="P41" s="14" t="n">
+        <v>10.8</v>
       </c>
       <c r="Q41" s="3" t="n">
         <v>29.8</v>
@@ -3925,24 +3921,24 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>22.2</v>
+        <v>122.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12.6</v>
+        <v>32.6</v>
       </c>
       <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="X41" s="14" t="n">
         <v>1.6</v>
       </c>
-      <c r="Y41" s="3" t="n">
-        <v>1828.4</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+      <c r="Y41" s="3" t="inlineStr"/>
+      <c r="Z41" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3959,23 +3955,23 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="8" t="n">
-        <v>12.1</v>
+      <c r="D42" s="13" t="n">
+        <v>31.2</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G42" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>12</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>7.3</v>
@@ -3983,32 +3979,32 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="14" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="14" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S42" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
@@ -4016,14 +4012,14 @@
       <c r="V42" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W42" s="3" t="n">
-        <v>13</v>
+      <c r="W42" s="14" t="n">
+        <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>12.8</v>
+        <v>22.8</v>
       </c>
       <c r="Z42" s="3" t="inlineStr"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -4040,22 +4036,22 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="D43" s="8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G43" s="8" t="n">
+        <v>534</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G43" s="14" t="n">
         <v>4.1</v>
       </c>
-      <c r="H43" s="8" t="n">
-        <v>13.4</v>
+      <c r="H43" s="14" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4069,14 +4065,14 @@
       <c r="L43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="8" t="n">
+      <c r="M43" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>921.6</v>
+        <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
@@ -4084,7 +4080,7 @@
       <c r="Q43" s="3" t="n">
         <v>28.9</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4094,13 +4090,13 @@
         <v>21.3</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>81.40000000000001</v>
+        <v>31.4</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4109,7 +4105,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>24.6</v>
+        <v>124.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4127,16 +4123,16 @@
       <c r="C44" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="F44" s="12" t="n">
+      <c r="D44" s="13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="F44" s="13" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G44" s="13" t="n">
         <v>15.7</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4149,19 +4145,19 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>19.8</v>
+        <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="P44" s="3" t="n">
         <v>10.6</v>
@@ -4169,33 +4165,31 @@
       <c r="Q44" s="3" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="8" t="n">
+      <c r="R44" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>7.8</v>
+        <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>119.3</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>12.8</v>
+        <v>112.3</v>
+      </c>
+      <c r="U44" s="14" t="n">
+        <v>22.8</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="W44" s="8" t="n">
+      <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="8" t="n">
-        <v>12.8</v>
+      <c r="X44" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>1122.1</v>
-      </c>
+        <v>50.8</v>
+      </c>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4209,72 +4203,72 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="10" t="n">
-        <v>1555.1</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>411.9</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>1102.1</v>
+      <c r="C45" s="3" t="n">
+        <v>1801.1</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="F45" s="9" t="n">
+        <v>1122.1</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>91.09999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>29.2</v>
+        <v>21.7</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>345</v>
+        <v>721.1</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>226.3</v>
+        <v>52.3</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>14.8</v>
+        <v>181.2</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>1291.9</v>
+        <v>1281.8</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>22.1</v>
+        <v>27.1</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>102261.5</v>
+        <v>1226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>920.4</v>
+        <v>28.4</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>128.4</v>
+        <v>170</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>11.8</v>
+        <v>81.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="U45" s="3" t="n">
-        <v>102.6</v>
-      </c>
+        <v>126.4</v>
+      </c>
+      <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="n">
-        <v>141.2</v>
+        <v>144.2</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>101</v>
+        <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>18.8</v>
+        <v>1.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>1222.4</v>
+        <v>1222.9</v>
       </c>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
@@ -4291,41 +4285,43 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>551.8</v>
-      </c>
-      <c r="D46" s="13" t="n">
-        <v>70.59999999999999</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>1</v>
+        <v>561.8</v>
+      </c>
+      <c r="D46" s="15" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>33</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>10.9</v>
+        <v>12.5</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="8" t="n">
+      <c r="M46" s="14" t="n">
         <v>80.8</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>119.4</v>
+        <v>49.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
@@ -4334,7 +4330,7 @@
         <v>28.8</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>9</v>
@@ -4343,22 +4339,22 @@
         <v>22.7</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>20.8</v>
+        <v>80.8</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W46" s="8" t="n">
-        <v>14.4</v>
+        <v>24</v>
+      </c>
+      <c r="W46" s="14" t="n">
+        <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.1</v>
+        <v>22.1</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>119.6</v>
+        <v>112.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -59,14 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,13 +152,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,10 +170,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,16 +792,16 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="12" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -813,7 +816,7 @@
       <c r="K4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="12" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
@@ -841,8 +844,8 @@
         <v>8.4</v>
       </c>
       <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
+      <c r="V4" s="13" t="inlineStr"/>
+      <c r="W4" s="13" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
       <c r="Z4" s="3" t="inlineStr"/>
@@ -862,16 +865,16 @@
       <c r="C5" s="3" t="n">
         <v>648.3</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>32.9</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="12" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -886,7 +889,7 @@
       <c r="K5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="12" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
@@ -904,7 +907,7 @@
       <c r="Q5" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="14" t="n">
+      <c r="R5" s="15" t="n">
         <v>84</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -947,16 +950,16 @@
       <c r="C6" s="3" t="n">
         <v>306.8</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>33.8</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="12" t="n">
         <v>10.7</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="12" t="n">
         <v>22.4</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
         <v>23.1</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -971,7 +974,7 @@
       <c r="K6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L6" s="14" t="n">
+      <c r="L6" s="12" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
@@ -998,13 +1001,13 @@
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="14" t="n">
+      <c r="U6" s="16" t="n">
         <v>91</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="15" t="n">
         <v>4.1</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1032,16 +1035,16 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>35.2</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <v>10.9</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="12" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1056,7 +1059,7 @@
       <c r="K7" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="12" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
@@ -1074,7 +1077,7 @@
       <c r="Q7" s="3" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="15" t="n">
         <v>3.2</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1089,7 +1092,7 @@
       <c r="V7" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="15" t="n">
         <v>0.3</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1117,13 +1120,13 @@
       <c r="C8" s="3" t="n">
         <v>285.1</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>34.4</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="12" t="n">
         <v>27.7</v>
       </c>
       <c r="G8" s="3" t="n">
@@ -1135,16 +1138,16 @@
       <c r="I8" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="16" t="n">
         <v>11</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="12" t="n">
         <v>19.9</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="16" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
@@ -1157,7 +1160,7 @@
       <c r="Q8" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="16" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1217,13 +1220,13 @@
       <c r="J9" s="3" t="n">
         <v>168.4</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>67.09999999999999</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="9" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1235,10 +1238,10 @@
       <c r="P9" s="3" t="n">
         <v>49.7</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="9" t="n">
         <v>169</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>71.8</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1250,10 +1253,10 @@
       <c r="U9" s="3" t="n">
         <v>1224.1</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="9" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1303,10 +1306,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="12" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="9" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1316,10 +1319,10 @@
       <c r="P10" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>14.4</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1331,10 +1334,10 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>13.9</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1362,16 +1365,16 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="12" t="n">
         <v>17.2</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="12" t="n">
         <v>23.9</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="H11" s="3" t="n">
@@ -1389,7 +1392,7 @@
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="12" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1416,8 +1419,8 @@
       <c r="U11" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
+      <c r="V11" s="13" t="inlineStr"/>
+      <c r="W11" s="13" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1440,8 +1443,8 @@
       <c r="D12" s="15" t="n">
         <v>51.3</v>
       </c>
-      <c r="E12" s="12" t="inlineStr"/>
-      <c r="F12" s="14" t="n">
+      <c r="E12" s="13" t="inlineStr"/>
+      <c r="F12" s="16" t="n">
         <v>21.7</v>
       </c>
       <c r="G12" s="3" t="n">
@@ -1462,7 +1465,7 @@
       <c r="L12" s="3" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="12" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1471,10 +1474,10 @@
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q12" s="16" t="n">
         <v>11.8</v>
       </c>
       <c r="R12" s="3" t="n">
@@ -1492,10 +1495,10 @@
       <c r="V12" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="W12" s="14" t="n">
+      <c r="W12" s="15" t="n">
         <v>84</v>
       </c>
-      <c r="X12" s="14" t="n">
+      <c r="X12" s="16" t="n">
         <v>62.3</v>
       </c>
       <c r="Y12" s="3" t="n">
@@ -1520,16 +1523,16 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="12" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="12" t="n">
         <v>18.9</v>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
@@ -1545,7 +1548,7 @@
       <c r="L13" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="12" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
@@ -1558,7 +1561,7 @@
       <c r="Q13" s="3" t="n">
         <v>33.2</v>
       </c>
-      <c r="R13" s="14" t="n">
+      <c r="R13" s="16" t="n">
         <v>15.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1601,13 +1604,13 @@
       <c r="C14" s="3" t="n">
         <v>489</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="G14" s="3" t="n">
@@ -1628,7 +1631,7 @@
       <c r="L14" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1643,7 +1646,7 @@
       <c r="Q14" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="15" t="n">
         <v>4.5</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1695,7 +1698,7 @@
       <c r="F15" s="15" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="16" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1713,7 +1716,7 @@
       <c r="L15" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="12" t="n">
         <v>10.4</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1728,8 +1731,8 @@
       <c r="Q15" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="14" t="n">
+      <c r="R15" s="13" t="inlineStr"/>
+      <c r="S15" s="16" t="n">
         <v>0.8</v>
       </c>
       <c r="T15" s="3" t="n">
@@ -1738,10 +1741,10 @@
       <c r="U15" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="15" t="n">
         <v>98.09999999999999</v>
       </c>
-      <c r="W15" s="14" t="n">
+      <c r="W15" s="16" t="n">
         <v>24</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1786,11 +1789,11 @@
       <c r="J16" s="3" t="n">
         <v>56.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="n">
+      <c r="L16" s="11" t="inlineStr"/>
+      <c r="M16" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1802,10 +1805,10 @@
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>184.7</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="9" t="n">
         <v>83.59999999999999</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1817,10 +1820,10 @@
       <c r="U16" s="3" t="n">
         <v>128.2</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="9" t="n">
         <v>131.3</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1875,7 +1878,7 @@
       <c r="L17" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="12" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1887,10 +1890,10 @@
       <c r="P17" s="3" t="n">
         <v>12.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1899,13 +1902,13 @@
       <c r="T17" s="3" t="n">
         <v>116.4</v>
       </c>
-      <c r="U17" s="14" t="n">
+      <c r="U17" s="16" t="n">
         <v>27.4</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>946.5</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1933,7 +1936,7 @@
       <c r="C18" s="3" t="n">
         <v>232.1</v>
       </c>
-      <c r="D18" s="14" t="n">
+      <c r="D18" s="16" t="n">
         <v>22.9</v>
       </c>
       <c r="E18" s="15" t="n">
@@ -1958,7 +1961,7 @@
       <c r="L18" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="M18" s="3" t="n">
+      <c r="M18" s="12" t="n">
         <v>7.6</v>
       </c>
       <c r="N18" s="3" t="n">
@@ -1970,10 +1973,10 @@
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="15" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -1985,10 +1988,10 @@
       <c r="U18" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V18" s="14" t="n">
+      <c r="V18" s="16" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="14" t="n">
+      <c r="W18" s="16" t="n">
         <v>14.4</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2016,16 +2019,16 @@
       <c r="C19" s="3" t="n">
         <v>596.1</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="12" t="n">
         <v>12.4</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="12" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2038,10 +2041,10 @@
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="3" t="n">
+      <c r="L19" s="15" t="n">
         <v>63.5</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="12" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2056,7 +2059,7 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="14" t="n">
+      <c r="R19" s="12" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2068,7 +2071,7 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="15" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="W19" s="3" t="n">
@@ -2123,13 +2126,13 @@
       <c r="K20" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L20" s="14" t="n">
+      <c r="L20" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="3" t="n">
+      <c r="M20" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="14" t="n">
+      <c r="N20" s="16" t="n">
         <v>19.1</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2141,7 +2144,7 @@
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="12" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2208,10 +2211,10 @@
       <c r="K21" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="L21" s="15" t="n">
         <v>75.7</v>
       </c>
-      <c r="M21" s="14" t="n">
+      <c r="M21" s="12" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2226,7 +2229,7 @@
       <c r="Q21" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="12" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2238,10 +2241,10 @@
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="14" t="n">
+      <c r="V21" s="15" t="n">
         <v>86.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2269,16 +2272,16 @@
       <c r="C22" s="3" t="n">
         <v>936.3</v>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="12" t="n">
         <v>31.8</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2296,7 +2299,7 @@
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="12" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
@@ -2311,7 +2314,7 @@
       <c r="Q22" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2320,10 +2323,10 @@
       <c r="T22" s="3" t="n">
         <v>184.9</v>
       </c>
-      <c r="U22" s="14" t="n">
+      <c r="U22" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="14" t="n">
+      <c r="V22" s="16" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2354,16 +2357,16 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="12" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="12" t="n">
         <v>73.5</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="12" t="n">
         <v>116.9</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2375,13 +2378,13 @@
       <c r="J23" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="9" t="n">
         <v>7.9</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="12" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2393,10 +2396,10 @@
       <c r="P23" s="3" t="n">
         <v>41.3</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="9" t="n">
         <v>254.4</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>23.5</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2408,10 +2411,10 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="9" t="n">
         <v>138.6</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="9" t="n">
         <v>68.8</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2439,32 +2442,32 @@
       <c r="C24" s="3" t="n">
         <v>503.5</v>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="12" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="12" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="12" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="16" t="n">
         <v>2.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="14" t="n">
+      <c r="J24" s="16" t="n">
         <v>17.4</v>
       </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="9" t="n">
         <v>15.8</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="9" t="n">
         <v>18.1</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2476,10 +2479,10 @@
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="9" t="n">
         <v>20.9</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="12" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2491,10 +2494,10 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>1.6</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2522,16 +2525,16 @@
       <c r="C25" s="3" t="n">
         <v>455.5</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>31.9</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="12" t="n">
         <v>17.7</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="12" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2543,13 +2546,13 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="14" t="n">
+      <c r="K25" s="16" t="n">
         <v>10.9</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="14" t="n">
+      <c r="M25" s="16" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2558,16 +2561,16 @@
       <c r="O25" s="3" t="n">
         <v>401</v>
       </c>
-      <c r="P25" s="14" t="n">
+      <c r="P25" s="16" t="n">
         <v>14</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="R25" s="14" t="n">
+      <c r="R25" s="12" t="n">
         <v>14.8</v>
       </c>
-      <c r="S25" s="14" t="n">
+      <c r="S25" s="16" t="n">
         <v>37.3</v>
       </c>
       <c r="T25" s="3" t="n">
@@ -2576,7 +2579,7 @@
       <c r="U25" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="15" t="n">
         <v>3.7</v>
       </c>
       <c r="W25" s="3" t="n">
@@ -2607,19 +2610,19 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="12" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="12" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="12" t="n">
         <v>22.6</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>85.5</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="16" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2631,10 +2634,10 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="14" t="n">
+      <c r="L26" s="16" t="n">
         <v>13.9</v>
       </c>
-      <c r="M26" s="14" t="n">
+      <c r="M26" s="16" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2646,10 +2649,10 @@
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="15" t="n">
         <v>99.3</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2664,7 +2667,7 @@
       <c r="V26" s="3" t="n">
         <v>26.7</v>
       </c>
-      <c r="W26" s="14" t="n">
+      <c r="W26" s="16" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2692,16 +2695,16 @@
       <c r="C27" s="3" t="n">
         <v>50.1</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="12" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="12" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="12" t="n">
         <v>23.5</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="12" t="n">
         <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
@@ -2710,7 +2713,7 @@
       <c r="I27" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="J27" s="14" t="n">
+      <c r="J27" s="16" t="n">
         <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
@@ -2734,7 +2737,7 @@
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="12" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2743,13 +2746,13 @@
       <c r="T27" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="U27" s="14" t="n">
+      <c r="U27" s="16" t="n">
         <v>17.4</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W27" s="3" t="n">
+      <c r="W27" s="15" t="n">
         <v>0.1</v>
       </c>
       <c r="X27" s="3" t="n">
@@ -2777,19 +2780,19 @@
       <c r="C28" s="3" t="n">
         <v>1621</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="12" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="12" t="n">
         <v>14.6</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="F28" s="12" t="n">
         <v>23.9</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>88.59999999999999</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="16" t="n">
         <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2813,13 +2816,13 @@
       <c r="O28" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="P28" s="14" t="n">
+      <c r="P28" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="3" t="n">
-        <v>803.9</v>
-      </c>
-      <c r="R28" s="3" t="n">
+      <c r="Q28" s="15" t="n">
+        <v>80.39</v>
+      </c>
+      <c r="R28" s="12" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2831,7 +2834,7 @@
       <c r="U28" s="3" t="n">
         <v>43.4</v>
       </c>
-      <c r="V28" s="14" t="n">
+      <c r="V28" s="16" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2860,16 +2863,16 @@
       <c r="C29" s="3" t="n">
         <v>624.8</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="12" t="n">
         <v>34.4</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="12" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="12" t="n">
         <v>23.3</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
         <v>22.2</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2881,7 +2884,7 @@
       <c r="J29" s="3" t="n">
         <v>49.3</v>
       </c>
-      <c r="K29" s="14" t="n">
+      <c r="K29" s="16" t="n">
         <v>181.1</v>
       </c>
       <c r="L29" s="3" t="n">
@@ -2899,10 +2902,10 @@
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q29" s="3" t="n">
+      <c r="Q29" s="15" t="n">
         <v>83.5</v>
       </c>
-      <c r="R29" s="14" t="n">
+      <c r="R29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2966,13 +2969,13 @@
       <c r="J30" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>118.9</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="9" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="9" t="n">
         <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -2984,10 +2987,10 @@
       <c r="P30" s="3" t="n">
         <v>91.7</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="9" t="n">
         <v>155.1</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="9" t="n">
         <v>0.9</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -2999,10 +3002,10 @@
       <c r="U30" s="3" t="n">
         <v>194.1</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="9" t="n">
         <v>166.8</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3030,16 +3033,16 @@
       <c r="C31" s="3" t="n">
         <v>236.4</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="12" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="12" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
         <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3054,10 +3057,10 @@
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="9" t="n">
         <v>16.4</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="9" t="n">
         <v>110.1</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3069,10 +3072,10 @@
       <c r="P31" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="12" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3084,10 +3087,10 @@
       <c r="U31" s="3" t="n">
         <v>38.8</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
@@ -3115,16 +3118,16 @@
       <c r="C32" s="3" t="n">
         <v>61.1</v>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="12" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="12" t="n">
         <v>20.6</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="12" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="12" t="n">
         <v>23.2</v>
       </c>
       <c r="H32" s="3" t="n">
@@ -3139,7 +3142,7 @@
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="15" t="n">
         <v>1.4</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3169,7 +3172,7 @@
       <c r="U32" s="3" t="n">
         <v>47.4</v>
       </c>
-      <c r="V32" s="14" t="n">
+      <c r="V32" s="16" t="n">
         <v>28.3</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3200,16 +3203,16 @@
       <c r="C33" s="3" t="n">
         <v>122.5</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="12" t="n">
         <v>31.5</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="12" t="n">
         <v>14.6</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="12" t="n">
         <v>22.8</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="12" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3227,7 +3230,7 @@
       <c r="L33" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="14" t="n">
+      <c r="M33" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
@@ -3251,7 +3254,7 @@
       <c r="T33" s="3" t="n">
         <v>30.3</v>
       </c>
-      <c r="U33" s="14" t="n">
+      <c r="U33" s="16" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
@@ -3260,7 +3263,7 @@
       <c r="W33" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="X33" s="14" t="n">
+      <c r="X33" s="16" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
@@ -3285,16 +3288,16 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="12" t="n">
         <v>15.6</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
@@ -3312,7 +3315,7 @@
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="14" t="n">
+      <c r="M34" s="15" t="n">
         <v>81.40000000000001</v>
       </c>
       <c r="N34" s="3" t="n">
@@ -3370,16 +3373,16 @@
       <c r="C35" s="3" t="n">
         <v>439.9</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="F35" s="12" t="n">
         <v>23.7</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="12" t="n">
         <v>13.3</v>
       </c>
       <c r="H35" s="3" t="n">
@@ -3409,7 +3412,7 @@
       <c r="P35" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="Q35" s="13" t="inlineStr"/>
       <c r="R35" s="3" t="n">
         <v>15.9</v>
       </c>
@@ -3454,23 +3457,23 @@
       <c r="D36" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="12" t="n">
         <v>11.9</v>
       </c>
-      <c r="F36" s="13" t="n">
+      <c r="F36" s="12" t="n">
         <v>18.7</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="H36" s="14" t="n">
+      <c r="H36" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
       </c>
@@ -3501,10 +3504,10 @@
       <c r="U36" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="15" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="W36" s="14" t="n">
+      <c r="W36" s="16" t="n">
         <v>13.6</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3553,13 +3556,13 @@
       <c r="J37" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="9" t="n">
         <v>3.6</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="9" t="n">
         <v>3.2</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3571,10 +3574,10 @@
       <c r="P37" s="3" t="n">
         <v>89.3</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="9" t="n">
         <v>133.5</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="9" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3586,10 +3589,10 @@
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="9" t="n">
         <v>114.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="9" t="n">
         <v>67</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3617,13 +3620,13 @@
       <c r="C38" s="3" t="n">
         <v>442.2</v>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="12" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F38" s="12" t="n">
         <v>22.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3641,10 +3644,10 @@
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="9" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3656,10 +3659,10 @@
       <c r="P38" s="3" t="n">
         <v>7.9</v>
       </c>
-      <c r="Q38" s="14" t="n">
+      <c r="Q38" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>14.8</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3671,10 +3674,10 @@
       <c r="U38" s="3" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="9" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3714,7 +3717,7 @@
       <c r="G39" s="15" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="H39" s="14" t="n">
+      <c r="H39" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
@@ -3726,7 +3729,7 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="14" t="n">
+      <c r="L39" s="12" t="n">
         <v>15.1</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3741,7 +3744,7 @@
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="3" t="n">
+      <c r="Q39" s="12" t="n">
         <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3753,16 +3756,16 @@
       <c r="T39" s="3" t="n">
         <v>22.4</v>
       </c>
-      <c r="U39" s="14" t="n">
+      <c r="U39" s="16" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="12" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="14" t="n">
+      <c r="X39" s="16" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
@@ -3787,19 +3790,19 @@
       <c r="C40" s="3" t="n">
         <v>641.4</v>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="12" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="13" t="n">
+      <c r="F40" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
@@ -3811,7 +3814,7 @@
       <c r="K40" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L40" s="14" t="n">
+      <c r="L40" s="12" t="n">
         <v>16.2</v>
       </c>
       <c r="M40" s="3" t="n">
@@ -3826,10 +3829,10 @@
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="3" t="n">
+      <c r="Q40" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="14" t="n">
+      <c r="R40" s="16" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3841,7 +3844,7 @@
       <c r="U40" s="3" t="n">
         <v>84.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="12" t="n">
         <v>26</v>
       </c>
       <c r="W40" s="3" t="n">
@@ -3872,16 +3875,16 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>31.4</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="12" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="13" t="n">
+      <c r="F41" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="12" t="n">
         <v>15.2</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3896,10 +3899,10 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="14" t="n">
+      <c r="L41" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="14" t="n">
+      <c r="M41" s="16" t="n">
         <v>11.9</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3908,10 +3911,10 @@
       <c r="O41" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P41" s="14" t="n">
+      <c r="P41" s="16" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="3" t="n">
+      <c r="Q41" s="12" t="n">
         <v>29.8</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3926,13 +3929,13 @@
       <c r="U41" s="3" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="12" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="X41" s="14" t="n">
+      <c r="X41" s="16" t="n">
         <v>1.6</v>
       </c>
       <c r="Y41" s="3" t="inlineStr"/>
@@ -3955,16 +3958,16 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="12" t="n">
         <v>31.2</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="12" t="n">
         <v>15.5</v>
       </c>
-      <c r="F42" s="13" t="n">
+      <c r="F42" s="12" t="n">
         <v>23.2</v>
       </c>
-      <c r="G42" s="14" t="n">
+      <c r="G42" s="16" t="n">
         <v>18.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3979,10 +3982,10 @@
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="14" t="n">
+      <c r="L42" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="14" t="n">
+      <c r="M42" s="16" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -3994,7 +3997,7 @@
       <c r="P42" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q42" s="3" t="n">
+      <c r="Q42" s="12" t="n">
         <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4009,10 +4012,10 @@
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="W42" s="14" t="n">
+      <c r="W42" s="16" t="n">
         <v>23</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4038,19 +4041,19 @@
       <c r="C43" s="3" t="n">
         <v>534</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>30.6</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="F43" s="12" t="n">
         <v>23.3</v>
       </c>
-      <c r="G43" s="14" t="n">
+      <c r="G43" s="16" t="n">
         <v>4.1</v>
       </c>
-      <c r="H43" s="14" t="n">
+      <c r="H43" s="16" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="I43" s="3" t="n">
@@ -4062,7 +4065,7 @@
       <c r="K43" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="12" t="n">
         <v>17.7</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4077,7 +4080,7 @@
       <c r="P43" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q43" s="3" t="n">
+      <c r="Q43" s="12" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4092,7 +4095,7 @@
       <c r="U43" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="12" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
@@ -4123,16 +4126,16 @@
       <c r="C44" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="12" t="n">
         <v>15.1</v>
       </c>
-      <c r="F44" s="13" t="n">
+      <c r="F44" s="12" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G44" s="12" t="n">
         <v>15.7</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4147,10 +4150,10 @@
       <c r="K44" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="12" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="3" t="n">
+      <c r="M44" s="15" t="n">
         <v>4.8</v>
       </c>
       <c r="N44" s="3" t="n">
@@ -4162,7 +4165,7 @@
       <c r="P44" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="3" t="n">
+      <c r="Q44" s="12" t="n">
         <v>29.2</v>
       </c>
       <c r="R44" s="3" t="n">
@@ -4174,10 +4177,10 @@
       <c r="T44" s="3" t="n">
         <v>112.3</v>
       </c>
-      <c r="U44" s="14" t="n">
+      <c r="U44" s="16" t="n">
         <v>22.8</v>
       </c>
-      <c r="V44" s="3" t="n">
+      <c r="V44" s="12" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4227,13 +4230,13 @@
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>181.2</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="9" t="n">
         <v>1281.8</v>
       </c>
-      <c r="M45" s="3" t="n">
+      <c r="M45" s="9" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4245,10 +4248,10 @@
       <c r="P45" s="3" t="n">
         <v>28.4</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="9" t="n">
         <v>170</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="9" t="n">
         <v>81.5</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4258,10 +4261,10 @@
         <v>126.4</v>
       </c>
       <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="9" t="n">
         <v>144.2</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="9" t="n">
         <v>28.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4311,10 +4314,10 @@
       <c r="K46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="12" t="n">
         <v>16.8</v>
       </c>
-      <c r="M46" s="14" t="n">
+      <c r="M46" s="9" t="n">
         <v>80.8</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4326,10 +4329,10 @@
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="3" t="n">
+      <c r="Q46" s="12" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>12</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4341,10 +4344,10 @@
       <c r="U46" s="3" t="n">
         <v>80.8</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="W46" s="14" t="n">
+      <c r="W46" s="9" t="n">
         <v>12.4</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -53,20 +59,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -152,13 +152,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -168,9 +171,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -792,20 +792,20 @@
       <c r="C4" s="3" t="n">
         <v>569.8</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
@@ -814,31 +814,31 @@
         <v>13.8</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="9" t="n">
         <v>11.1</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>23.7</v>
+        <v>1.1</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>34.5</v>
+        <v>35.5</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>8.5</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="R4" s="3" t="n">
+      <c r="Q4" s="9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="R4" s="9" t="n">
         <v>13.7</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>4.3</v>
+        <v>11.3</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8.4</v>
@@ -863,18 +863,18 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>648.3</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E5" s="12" t="n">
+        <v>512.7</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="F5" s="12" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="G5" s="12" t="n">
+      <c r="F5" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G5" s="9" t="n">
         <v>21.8</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -887,49 +887,47 @@
         <v>12.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L5" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>15.5</v>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="n">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="R5" s="15" t="n">
-        <v>84</v>
+      <c r="R5" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>5.7</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="U5" s="3" t="n">
-        <v>16.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="U5" s="16" t="n">
+        <v>46.8</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>28.4</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>12.3</v>
+        <v>13.3</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>26.8</v>
+        <v>96.8</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>32.2</v>
@@ -948,67 +946,65 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>306.8</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>33.8</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>23.1</v>
+        <v>504.8</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>23.9</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>7.5</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>13.2</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
         <v>12.2</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="3" t="n">
-        <v>2.8</v>
-      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="n">
-        <v>100.8</v>
+        <v>140</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q6" s="9" t="n">
         <v>32.7</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>15.2</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="U6" s="16" t="n">
-        <v>91</v>
+      <c r="U6" s="3" t="n">
+        <v>41</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W6" s="15" t="n">
-        <v>4.1</v>
+      <c r="W6" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="X6" s="3" t="n">
         <v>8.1</v>
@@ -1017,7 +1013,7 @@
         <v>21.2</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>20.2</v>
+        <v>230.2</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1035,20 +1031,20 @@
       <c r="C7" s="3" t="n">
         <v>583.6</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="D7" s="9" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" s="9" t="n">
         <v>23.1</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>11.3</v>
@@ -1057,52 +1053,50 @@
         <v>16.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L7" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="L7" s="9" t="n">
         <v>12.5</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N7" s="3" t="n">
-        <v>1.1</v>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="n">
         <v>35</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="Q7" s="3" t="n">
+      <c r="Q7" s="9" t="n">
         <v>34.7</v>
       </c>
-      <c r="R7" s="15" t="n">
-        <v>3.2</v>
+      <c r="R7" s="9" t="n">
+        <v>13.8</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3.6</v>
+        <v>13.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>6.6</v>
+        <v>14.4</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>21.7</v>
+        <v>42.4</v>
       </c>
       <c r="V7" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="Z7" s="3" t="n">
         <v>29.1</v>
-      </c>
-      <c r="W7" s="15" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="Z7" s="3" t="n">
-        <v>2.8</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1118,49 +1112,49 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>285.1</v>
-      </c>
-      <c r="D8" s="12" t="n">
+        <v>485.1</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>34.4</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="G8" s="3" t="n">
+      <c r="E8" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>23.4</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="M8" s="16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>10.8</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>3262</v>
+        <v>36.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="9" t="n">
         <v>32.6</v>
       </c>
-      <c r="R8" s="16" t="n">
+      <c r="R8" s="9" t="n">
         <v>15.1</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1170,21 +1164,23 @@
         <v>14.3</v>
       </c>
       <c r="U8" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="V8" s="12" t="n">
         <v>42.2</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>15.3</v>
+      <c r="W8" s="16" t="n">
+        <v>13.3</v>
       </c>
       <c r="X8" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="Y8" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1199,71 +1195,73 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>19656.5</v>
+        <v>2636.1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1169.7</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>38.3</v>
-      </c>
-      <c r="F9" s="11" t="inlineStr"/>
-      <c r="G9" s="15" t="n">
+        <v>169.7</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>123.3</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>1113.4</v>
+      </c>
+      <c r="G9" s="12" t="n">
         <v>11.6</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>39.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>14.2</v>
+        <v>44.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>168.4</v>
-      </c>
-      <c r="K9" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L9" s="9" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="M9" s="9" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>167.1</v>
+      </c>
+      <c r="M9" s="15" t="n">
         <v>32.5</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>121.7</v>
+        <v>2.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>183</v>
+        <v>1183</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>169</v>
-      </c>
-      <c r="R9" s="9" t="n">
-        <v>71.8</v>
+        <v>165</v>
+      </c>
+      <c r="R9" s="15" t="n">
+        <v>171.8</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>27.7</v>
+        <v>127.7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>1224.1</v>
-      </c>
-      <c r="V9" s="9" t="n">
+        <v>224.8</v>
+      </c>
+      <c r="V9" s="15" t="n">
         <v>139.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="15" t="n">
         <v>169.6</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>28.9</v>
+        <v>38.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1186.2</v>
+        <v>10.6</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>120.2</v>
@@ -1285,19 +1283,19 @@
         <v>531.2</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>23.9</v>
+        <v>34.4</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="G10" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G10" s="16" t="n">
         <v>23.2</v>
       </c>
-      <c r="H10" s="3" t="n">
-        <v>2.3</v>
+      <c r="H10" s="16" t="n">
+        <v>47.8</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>8.800000000000001</v>
@@ -1306,10 +1304,10 @@
         <v>13.7</v>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="9" t="n">
         <v>13.4</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="15" t="n">
         <v>6.5</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
@@ -1317,7 +1315,7 @@
         <v>36.6</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>33</v>
@@ -1334,20 +1332,20 @@
       <c r="U10" s="3" t="n">
         <v>44.8</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="15" t="n">
         <v>27.9</v>
       </c>
-      <c r="W10" s="9" t="n">
-        <v>13.9</v>
+      <c r="W10" s="15" t="n">
+        <v>19.9</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>87.8</v>
+        <v>17.8</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>21.2</v>
+        <v>1106.2</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1365,62 +1363,64 @@
       <c r="C11" s="3" t="n">
         <v>427.9</v>
       </c>
-      <c r="D11" s="12" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E11" s="12" t="n">
+      <c r="D11" s="3" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="G11" s="12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="I11" s="3" t="n">
-        <v>16.5</v>
+      <c r="I11" s="16" t="n">
+        <v>46.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L11" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L11" s="9" t="n">
         <v>18.2</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="3" t="n">
         <v>6.4</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="S11" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="V11" s="13" t="inlineStr"/>
-      <c r="W11" s="13" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="U11" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="W11" s="9" t="inlineStr"/>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="inlineStr"/>
       <c r="Z11" s="3" t="inlineStr"/>
@@ -1440,14 +1440,14 @@
       <c r="C12" s="3" t="n">
         <v>206.7</v>
       </c>
-      <c r="D12" s="15" t="n">
-        <v>51.3</v>
+      <c r="D12" s="3" t="n">
+        <v>31.1</v>
       </c>
       <c r="E12" s="13" t="inlineStr"/>
       <c r="F12" s="16" t="n">
         <v>21.7</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="16" t="n">
         <v>19.9</v>
       </c>
       <c r="H12" s="3" t="n">
@@ -1459,53 +1459,53 @@
       <c r="J12" s="3" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3" t="n">
+      <c r="K12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="n">
         <v>18.5</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" s="3" t="n">
         <v>12.7</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>1.1</v>
+        <v>11.1</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>53</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="16" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>14.4</v>
+        <v>20</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="R12" s="12" t="n">
+        <v>4.4</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16</v>
+        <v>6.5</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="U12" s="3" t="n">
+      <c r="U12" s="16" t="n">
         <v>29.2</v>
       </c>
-      <c r="V12" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="W12" s="15" t="n">
-        <v>84</v>
+      <c r="V12" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="W12" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="X12" s="16" t="n">
-        <v>62.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1417</v>
+        <v>47</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>18.8</v>
+        <v>13.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1523,46 +1523,48 @@
       <c r="C13" s="3" t="n">
         <v>601.3</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="9" t="n">
         <v>34.3</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="E13" s="9" t="n">
         <v>15.5</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="9" t="n">
         <v>18.9</v>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="16" t="n">
+        <v>11.4</v>
+      </c>
       <c r="I13" s="3" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="n">
-        <v>849</v>
+        <v>49</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>33.2</v>
       </c>
       <c r="R13" s="16" t="n">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="S13" s="3" t="n">
         <v>6.9</v>
@@ -1570,23 +1572,23 @@
       <c r="T13" s="3" t="n">
         <v>13.5</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="V13" s="3" t="n">
+      <c r="U13" s="16" t="n">
+        <v>49</v>
+      </c>
+      <c r="V13" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="9" t="n">
         <v>15.1</v>
       </c>
       <c r="X13" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>0.2</v>
+        <v>28.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>3.5</v>
+        <v>25.4</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1602,18 +1604,18 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>489</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E14" s="12" t="n">
+        <v>488</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="F14" s="12" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="G14" s="3" t="n">
+      <c r="F14" s="9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>14.4</v>
       </c>
       <c r="H14" s="3" t="n">
@@ -1625,53 +1627,51 @@
       <c r="J14" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="3" t="n">
+      <c r="K14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="n">
         <v>20.1</v>
       </c>
-      <c r="M14" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="M14" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
       <c r="O14" s="3" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="R14" s="15" t="n">
-        <v>4.5</v>
+      <c r="R14" s="16" t="n">
+        <v>14.5</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>73.8</v>
+        <v>7.3</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="U14" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="V14" s="3" t="n">
+      <c r="U14" s="16" t="n">
+        <v>236</v>
+      </c>
+      <c r="V14" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>1020.8</v>
+        <v>20.8</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>231.2</v>
+        <v>114.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1687,18 +1687,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2652.1</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="G15" s="16" t="n">
+        <v>552.9</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="G15" s="9" t="n">
         <v>16.3</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1710,48 +1710,52 @@
       <c r="J15" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="M15" s="16" t="n">
         <v>10.4</v>
       </c>
-      <c r="N15" s="3" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="n">
-        <v>148.8</v>
+        <v>418</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="R15" s="13" t="inlineStr"/>
-      <c r="S15" s="16" t="n">
-        <v>0.8</v>
+      <c r="R15" s="16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>16.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>15.4</v>
+        <v>115.4</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V15" s="15" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="W15" s="16" t="n">
-        <v>24</v>
+        <v>38</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>23.4</v>
+      </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>10</t>
@@ -1766,74 +1770,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>257.2</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>8291.6</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>1118.2</v>
+        <v>237.7</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>1291.6</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>2118.2</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>82.8</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>61.8</v>
+        <v>161.8</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>97.3</v>
+        <v>397.3</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>56.2</v>
+        <v>136.2</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="9" t="n">
-        <v>22.1</v>
+      <c r="L16" s="15" t="n">
+        <v>880.9</v>
+      </c>
+      <c r="M16" s="15" t="n">
+        <v>52.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>2212.5</v>
+        <v>212.5</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>62.2</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>184.7</v>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>83.59999999999999</v>
+        <v>154.7</v>
+      </c>
+      <c r="R16" s="15" t="n">
+        <v>173.6</v>
       </c>
       <c r="S16" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>128.2</v>
+        <v>188.2</v>
       </c>
       <c r="V16" s="9" t="n">
         <v>131.3</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>22.8</v>
+      <c r="W16" s="15" t="n">
+        <v>12.8</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>48.3</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>145.8</v>
+        <v>1145.8</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>1024.4</v>
+        <v>1224.4</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1849,43 +1855,43 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2313.4</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="F17" s="9" t="n">
+        <v>315.4</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F17" s="15" t="n">
         <v>23.6</v>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G17" s="16" t="n">
         <v>18.5</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L17" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="M17" s="15" t="n">
         <v>10.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>12.4</v>
@@ -1893,20 +1899,20 @@
       <c r="Q17" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="15" t="n">
         <v>14.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>7.3</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>116.4</v>
-      </c>
-      <c r="U17" s="16" t="n">
-        <v>27.4</v>
+        <v>16.4</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>37.6</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>946.5</v>
+        <v>26.3</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>14.5</v>
@@ -1918,7 +1924,7 @@
         <v>29.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>29.9</v>
+        <v>24.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1934,74 +1940,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>232.1</v>
-      </c>
-      <c r="D18" s="16" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+        <v>252.1</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>20.5</v>
+      </c>
       <c r="H18" s="3" t="n">
-        <v>15.4</v>
+        <v>12.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="3" t="n">
-        <v>13.5</v>
+      <c r="L18" s="16" t="n">
+        <v>18.5</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>7.6</v>
+        <v>2.6</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>17.5</v>
+        <v>137.5</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q18" s="15" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="R18" s="12" t="n">
+      <c r="Q18" s="16" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R18" s="3" t="n">
         <v>15.2</v>
       </c>
       <c r="S18" s="3" t="n">
         <v>7.4</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>118.3</v>
+        <v>115.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V18" s="16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.1</v>
       </c>
-      <c r="W18" s="16" t="n">
-        <v>14.4</v>
+      <c r="W18" s="12" t="n">
+        <v>84.40000000000001</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>0.8</v>
+        <v>8.4</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>22</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>292.8</v>
+        <v>29.2</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2017,41 +2023,43 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>596.1</v>
-      </c>
-      <c r="D19" s="12" t="n">
+        <v>326.4</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>33.5</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="9" t="n">
         <v>21.1</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="n">
-        <v>12.6</v>
+      <c r="I19" s="3" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="J19" s="16" t="n">
+        <v>20.6</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L19" s="15" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="M19" s="12" t="n">
+      <c r="L19" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="M19" s="3" t="n">
         <v>7.9</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>0.7</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>60.5</v>
+        <v>160.5</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>6</v>
@@ -2059,7 +2067,7 @@
       <c r="Q19" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="R19" s="12" t="n">
+      <c r="R19" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2071,20 +2079,20 @@
       <c r="U19" s="3" t="n">
         <v>41.4</v>
       </c>
-      <c r="V19" s="15" t="n">
-        <v>96.90000000000001</v>
+      <c r="V19" s="16" t="n">
+        <v>26.9</v>
       </c>
       <c r="W19" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>292.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2100,16 +2108,16 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>322.8</v>
-      </c>
-      <c r="D20" s="15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>12.3</v>
+        <v>322.5</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>20.3</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>14.1</v>
@@ -2124,16 +2132,16 @@
         <v>8.4</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.7</v>
+        <v>10.7</v>
       </c>
       <c r="L20" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="N20" s="16" t="n">
-        <v>19.1</v>
+      <c r="N20" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>55</v>
@@ -2144,32 +2152,32 @@
       <c r="Q20" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R20" s="12" t="n">
+      <c r="R20" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>44.8</v>
+        <v>22.5</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="W20" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="W20" s="16" t="n">
         <v>12.4</v>
       </c>
       <c r="X20" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>118.2</v>
+        <v>28.7</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2187,20 +2195,20 @@
       <c r="C21" s="3" t="n">
         <v>42.2</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="E21" s="15" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G21" s="3" t="n">
+      <c r="E21" s="9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G21" s="9" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>11.3</v>
+        <v>1.3</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>6.3</v>
@@ -2209,19 +2217,19 @@
         <v>10.6</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L21" s="15" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="M21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="M21" s="3" t="n">
         <v>11.5</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>10.3</v>
@@ -2229,23 +2237,23 @@
       <c r="Q21" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R21" s="12" t="n">
+      <c r="R21" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>7.6</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>17.2</v>
+        <v>117.2</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>36.6</v>
       </c>
-      <c r="V21" s="15" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="W21" s="15" t="n">
-        <v>0.4</v>
+      <c r="V21" s="3" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>14.5</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>9.6</v>
@@ -2254,7 +2262,7 @@
         <v>28</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>24.6</v>
+        <v>118.2</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2270,18 +2278,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>936.3</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="E22" s="12" t="n">
+        <v>536.3</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="E22" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="F22" s="12" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G22" s="12" t="n">
+      <c r="F22" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2290,50 +2298,48 @@
       <c r="I22" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="J22" s="3" t="n">
+      <c r="J22" s="16" t="n">
         <v>12.8</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>16.4</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="M22" s="16" t="n">
         <v>10.7</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O22" s="3" t="n">
-        <v>51</v>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
       <c r="P22" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>31.3</v>
       </c>
-      <c r="R22" s="12" t="n">
+      <c r="R22" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>6.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>184.9</v>
+        <v>114.9</v>
       </c>
       <c r="U22" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="V22" s="16" t="n">
+      <c r="V22" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="X22" s="3" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>26.3</v>
@@ -2357,16 +2363,16 @@
       <c r="C23" s="3" t="n">
         <v>2517.5</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="15" t="n">
         <v>160.3</v>
       </c>
-      <c r="E23" s="12" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>116.9</v>
-      </c>
-      <c r="G23" s="12" t="n">
+      <c r="E23" s="15" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="G23" s="3" t="n">
         <v>86.8</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2378,32 +2384,30 @@
       <c r="J23" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="15" t="n">
         <v>3.3</v>
       </c>
-      <c r="L23" s="9" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M23" s="12" t="n">
+      <c r="L23" s="15" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="M23" s="15" t="n">
         <v>50.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>1272</v>
+        <v>272</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="Q23" s="9" t="n">
-        <v>254.4</v>
-      </c>
-      <c r="R23" s="9" t="n">
-        <v>23.5</v>
-      </c>
+        <v>41.2</v>
+      </c>
+      <c r="Q23" s="15" t="n">
+        <v>154.4</v>
+      </c>
+      <c r="R23" s="14" t="inlineStr"/>
       <c r="S23" s="3" t="n">
-        <v>368.6</v>
+        <v>36.6</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>82.90000000000001</v>
@@ -2411,20 +2415,20 @@
       <c r="U23" s="3" t="n">
         <v>187.2</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>138.6</v>
-      </c>
-      <c r="W23" s="9" t="n">
-        <v>68.8</v>
+      <c r="V23" s="15" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="W23" s="15" t="n">
+        <v>168.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>42.8</v>
+        <v>142.8</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>127.3</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1122.4</v>
+        <v>127.4</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2440,49 +2444,51 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>503.5</v>
-      </c>
-      <c r="D24" s="12" t="n">
+        <v>509.5</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>32.1</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="9" t="n">
         <v>23.4</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="9" t="n">
         <v>17.4</v>
       </c>
-      <c r="H24" s="16" t="n">
-        <v>2.2</v>
+      <c r="H24" s="3" t="n">
+        <v>12.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="J24" s="16" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="9" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M24" s="9" t="n">
-        <v>18.1</v>
+      <c r="J24" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="M24" s="15" t="n">
+        <v>10.1</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>24.6</v>
+        <v>294.6</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="Q24" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="R24" s="12" t="n">
+      <c r="Q24" s="15" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>14.7</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2494,11 +2500,11 @@
       <c r="U24" s="3" t="n">
         <v>37.4</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="15" t="n">
         <v>26.1</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>1.6</v>
+      <c r="W24" s="15" t="n">
+        <v>13.8</v>
       </c>
       <c r="X24" s="3" t="n">
         <v>8.6</v>
@@ -2523,18 +2529,18 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>455.5</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="F25" s="12" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="F25" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G25" s="9" t="n">
         <v>14.2</v>
       </c>
       <c r="H25" s="3" t="n">
@@ -2546,53 +2552,53 @@
       <c r="J25" s="3" t="n">
         <v>9.9</v>
       </c>
-      <c r="K25" s="16" t="n">
+      <c r="K25" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="M25" s="16" t="n">
+      <c r="M25" s="9" t="n">
         <v>11.8</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>401</v>
+        <v>40</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
       <c r="Q25" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R25" s="3" t="n">
         <v>29.4</v>
       </c>
-      <c r="R25" s="12" t="n">
+      <c r="S25" s="16" t="n">
         <v>14.8</v>
       </c>
-      <c r="S25" s="16" t="n">
-        <v>37.3</v>
-      </c>
       <c r="T25" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="V25" s="15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="W25" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U25" s="16" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="V25" s="9" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="W25" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="X25" s="3" t="n">
+      <c r="X25" s="16" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="Y25" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y25" s="3" t="n">
-        <v>41.6</v>
-      </c>
       <c r="Z25" s="3" t="n">
-        <v>1112.1</v>
+        <v>457.3</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2610,19 +2616,19 @@
       <c r="C26" s="3" t="n">
         <v>530.4</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="9" t="n">
         <v>30.3</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="9" t="n">
         <v>14.8</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="H26" s="16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2634,10 +2640,10 @@
       <c r="K26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L26" s="16" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="M26" s="16" t="n">
+      <c r="L26" s="9" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="M26" s="9" t="n">
         <v>10.5</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2649,10 +2655,10 @@
       <c r="P26" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="Q26" s="15" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="R26" s="12" t="n">
+      <c r="Q26" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2661,23 +2667,23 @@
       <c r="T26" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="U26" s="3" t="n">
+      <c r="U26" s="16" t="n">
         <v>33.4</v>
       </c>
-      <c r="V26" s="3" t="n">
-        <v>26.7</v>
+      <c r="V26" s="9" t="n">
+        <v>26.4</v>
       </c>
       <c r="W26" s="16" t="n">
         <v>14.4</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>9.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>22</v>
+        <v>222</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.1</v>
+        <v>25</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2693,76 +2699,76 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="D27" s="12" t="n">
+        <v>550.1</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>31.8</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="9" t="n">
         <v>23.5</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="G27" s="9" t="n">
         <v>16.6</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J27" s="16" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="J27" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="9" t="n">
         <v>16.3</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>98.90000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>30.8</v>
       </c>
-      <c r="R27" s="12" t="n">
+      <c r="R27" s="16" t="n">
         <v>14.5</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>7.1</v>
+        <v>1.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="U27" s="16" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>28.2</v>
-      </c>
-      <c r="W27" s="15" t="n">
-        <v>0.1</v>
+        <v>116</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="V27" s="9" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>14.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>9.6</v>
+        <v>19.6</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>126.6</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>196.5</v>
+        <v>26.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2778,75 +2784,77 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1621</v>
-      </c>
-      <c r="D28" s="12" t="n">
+        <v>621</v>
+      </c>
+      <c r="D28" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="9" t="n">
         <v>23.9</v>
       </c>
-      <c r="G28" s="3" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="H28" s="16" t="n">
+      <c r="G28" s="16" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H28" s="3" t="n">
         <v>10.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>8.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>12.6</v>
+        <v>11</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="9" t="n">
         <v>16.5</v>
       </c>
-      <c r="M28" s="3" t="n">
+      <c r="M28" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="P28" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="Q28" s="15" t="n">
-        <v>80.39</v>
-      </c>
-      <c r="R28" s="12" t="n">
+      <c r="Q28" s="3" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="R28" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>29.4</v>
+        <v>598.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="V28" s="16" t="n">
+        <v>93.40000000000001</v>
+      </c>
+      <c r="V28" s="9" t="n">
         <v>27.7</v>
       </c>
       <c r="W28" s="3" t="n">
         <v>13.3</v>
       </c>
       <c r="X28" s="3" t="n">
-        <v>16.9</v>
+        <v>6.9</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="Z28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="n">
+        <v>20.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2861,19 +2869,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>624.8</v>
+        <v>624.9</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="E29" s="12" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E29" s="9" t="n">
         <v>12.2</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>22.2</v>
+      <c r="F29" s="16" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>0.2</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>7.6</v>
@@ -2882,15 +2890,15 @@
         <v>8.699999999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="K29" s="16" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="L29" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="n">
         <v>13.7</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="9" t="n">
         <v>7.3</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2902,10 +2910,10 @@
       <c r="P29" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q29" s="15" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="R29" s="12" t="n">
+      <c r="Q29" s="3" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="R29" s="16" t="n">
         <v>14</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2914,14 +2922,14 @@
       <c r="T29" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="U29" s="3" t="n">
+      <c r="U29" s="16" t="n">
         <v>47.1</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>13.3</v>
+      <c r="W29" s="12" t="n">
+        <v>3.3</v>
       </c>
       <c r="X29" s="3" t="n">
         <v>6.9</v>
@@ -2930,7 +2938,7 @@
         <v>18.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>23009</v>
+        <v>30.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2946,58 +2954,58 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>2281.9</v>
+        <v>2781.9</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>1561.6</v>
+        <v>161.6</v>
       </c>
       <c r="E30" s="9" t="n">
-        <v>714.5</v>
+        <v>74.5</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="G30" s="9" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1</v>
+        <v>237</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>118.9</v>
+        <v>135.8</v>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>18.9</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>82.2</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="15" t="n">
         <v>30.6</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>4.3</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>222.3</v>
+        <v>232.3</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>91.7</v>
       </c>
-      <c r="Q30" s="9" t="n">
-        <v>155.1</v>
-      </c>
-      <c r="R30" s="9" t="n">
-        <v>0.9</v>
+      <c r="Q30" s="15" t="n">
+        <v>153.1</v>
+      </c>
+      <c r="R30" s="15" t="n">
+        <v>20.9</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>82.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="U30" s="3" t="n">
         <v>194.1</v>
@@ -3005,17 +3013,15 @@
       <c r="V30" s="9" t="n">
         <v>126.7</v>
       </c>
-      <c r="W30" s="9" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>110</v>
-      </c>
+      <c r="W30" s="15" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>106.9</v>
+        <v>12.6</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>4.8</v>
+        <v>122.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3031,18 +3037,18 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>236.4</v>
-      </c>
-      <c r="D31" s="12" t="n">
+        <v>336.4</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="9" t="n">
         <v>14.9</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="F31" s="9" t="n">
         <v>23.6</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="G31" s="9" t="n">
         <v>17.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3051,7 +3057,7 @@
       <c r="I31" s="3" t="n">
         <v>7.4</v>
       </c>
-      <c r="J31" s="3" t="n">
+      <c r="J31" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="K31" s="3" t="n">
@@ -3061,7 +3067,7 @@
         <v>16.4</v>
       </c>
       <c r="M31" s="9" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>0.8</v>
@@ -3069,17 +3075,17 @@
       <c r="O31" s="3" t="n">
         <v>46.5</v>
       </c>
-      <c r="P31" s="3" t="n">
+      <c r="P31" s="16" t="n">
         <v>10.3</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="15" t="n">
         <v>31</v>
       </c>
-      <c r="R31" s="12" t="n">
+      <c r="R31" s="15" t="n">
         <v>14.2</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>6.9</v>
+        <v>2</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>14.5</v>
@@ -3090,14 +3096,14 @@
       <c r="V31" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="W31" s="9" t="n">
+      <c r="W31" s="15" t="n">
         <v>13.4</v>
       </c>
       <c r="X31" s="3" t="n">
         <v>8.4</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>0.2</v>
+        <v>127.3</v>
       </c>
       <c r="Z31" s="3" t="n">
         <v>24.6</v>
@@ -3116,23 +3122,21 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="D32" s="12" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="D32" s="9" t="n">
         <v>33.8</v>
       </c>
-      <c r="E32" s="12" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F32" s="12" t="n">
+      <c r="E32" s="9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F32" s="9" t="n">
         <v>22.2</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>6.2</v>
-      </c>
+      <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -3140,52 +3144,50 @@
         <v>13.2</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="15" t="n">
-        <v>1.4</v>
+        <v>10</v>
+      </c>
+      <c r="L32" s="16" t="n">
+        <v>16</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>39</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Q32" s="9" t="n">
         <v>33.6</v>
       </c>
       <c r="R32" s="3" t="n">
         <v>14.1</v>
       </c>
       <c r="S32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>1141.1</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr"/>
+      <c r="V32" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="T32" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="V32" s="16" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="W32" s="3" t="n">
+      <c r="W32" s="12" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>484.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
         <v>13.7</v>
-      </c>
-      <c r="X32" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y32" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>31.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3201,25 +3203,25 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="D33" s="12" t="n">
+        <v>443.7</v>
+      </c>
+      <c r="D33" s="9" t="n">
         <v>31.5</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="9" t="n">
         <v>14.6</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="9" t="n">
         <v>22.8</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="G33" s="9" t="n">
         <v>16.7</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>5.8</v>
@@ -3227,14 +3229,14 @@
       <c r="K33" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="16" t="n">
         <v>18.7</v>
       </c>
-      <c r="M33" s="16" t="n">
+      <c r="M33" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>41</v>
@@ -3242,10 +3244,10 @@
       <c r="P33" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="Q33" s="3" t="n">
+      <c r="Q33" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="16" t="n">
         <v>14.7</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3255,22 +3257,22 @@
         <v>30.3</v>
       </c>
       <c r="U33" s="16" t="n">
-        <v>93.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="V33" s="3" t="n">
         <v>21</v>
       </c>
       <c r="W33" s="3" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="X33" s="16" t="n">
         <v>11.1</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>149.2</v>
+        <v>1420.9</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>43.2</v>
+        <v>113.9</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3288,23 +3290,23 @@
       <c r="C34" s="3" t="n">
         <v>386.6</v>
       </c>
-      <c r="D34" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="F34" s="12" t="n">
+      <c r="D34" s="9" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F34" s="9" t="n">
         <v>23.2</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="16" t="n">
         <v>15.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.2</v>
+        <v>12.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>2.5</v>
+        <v>11</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.4</v>
@@ -3315,11 +3317,11 @@
       <c r="L34" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="M34" s="15" t="n">
-        <v>81.40000000000001</v>
+      <c r="M34" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>22.2</v>
@@ -3327,35 +3329,35 @@
       <c r="P34" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q34" s="3" t="n">
+      <c r="Q34" s="9" t="n">
         <v>19</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>12.4</v>
+        <v>13.4</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>12.9</v>
+        <v>12.1</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>9.9</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="X34" s="3" t="n">
-        <v>1.8</v>
+        <v>12.7</v>
+      </c>
+      <c r="X34" s="16" t="n">
+        <v>11.8</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>1801.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3371,31 +3373,31 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>439.9</v>
-      </c>
-      <c r="D35" s="12" t="n">
+        <v>433.9</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E35" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="G35" s="12" t="n">
+      <c r="E35" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F35" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G35" s="9" t="n">
         <v>13.3</v>
       </c>
-      <c r="H35" s="3" t="n">
+      <c r="H35" s="16" t="n">
         <v>14.9</v>
       </c>
       <c r="I35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>14.3</v>
+        <v>47.1</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>18.2</v>
@@ -3404,7 +3406,7 @@
         <v>12.6</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>18.1</v>
+        <v>1.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>24</v>
@@ -3412,18 +3414,20 @@
       <c r="P35" s="3" t="n">
         <v>98.59999999999999</v>
       </c>
-      <c r="Q35" s="13" t="inlineStr"/>
-      <c r="R35" s="3" t="n">
-        <v>15.9</v>
+      <c r="Q35" s="9" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="R35" s="12" t="n">
+        <v>58.9</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="U35" s="3" t="n">
-        <v>23.4</v>
+        <v>33.4</v>
       </c>
       <c r="V35" s="3" t="n">
         <v>23.5</v>
@@ -3435,9 +3439,11 @@
         <v>19.7</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>2121.5</v>
-      </c>
-      <c r="Z35" s="3" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -3454,25 +3460,27 @@
       <c r="C36" s="3" t="n">
         <v>341.3</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H36" s="16" t="n">
+      <c r="D36" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F36" s="9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H36" s="3" t="n">
         <v>11.2</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="K36" s="13" t="inlineStr"/>
       <c r="L36" s="3" t="n">
         <v>17.8</v>
@@ -3484,40 +3492,40 @@
         <v>1.1</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Q36" s="3" t="n">
+      <c r="Q36" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>14.5</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>11.7</v>
+        <v>10.7</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>2.4</v>
+        <v>34.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="V36" s="15" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="V36" s="12" t="n">
         <v>82.09999999999999</v>
       </c>
-      <c r="W36" s="16" t="n">
+      <c r="W36" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="X36" s="3" t="n">
-        <v>10.6</v>
+      <c r="X36" s="16" t="n">
+        <v>80.59999999999999</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>1186</v>
+        <v>146.6</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>116.8</v>
+        <v>126.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3535,74 +3543,72 @@
       <c r="C37" s="3" t="n">
         <v>2216.6</v>
       </c>
-      <c r="D37" s="9" t="n">
-        <v>11810.6</v>
-      </c>
-      <c r="E37" s="9" t="n">
+      <c r="D37" s="15" t="n">
+        <v>131.6</v>
+      </c>
+      <c r="E37" s="15" t="n">
         <v>168.9</v>
       </c>
-      <c r="F37" s="9" t="n">
-        <v>110.2</v>
+      <c r="F37" s="15" t="n">
+        <v>110.3</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>82.7</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>33.8</v>
+        <v>55.8</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="K37" s="15" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="L37" s="15" t="n">
         <v>81.90000000000001</v>
       </c>
-      <c r="M37" s="9" t="n">
-        <v>3.2</v>
+      <c r="M37" s="15" t="n">
+        <v>153.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>4.7</v>
+        <v>44.7</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>1240.2</v>
+        <v>2409.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>133.5</v>
-      </c>
-      <c r="R37" s="9" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="Q37" s="15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="R37" s="15" t="n">
         <v>82.59999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
         <v>147.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>1151</v>
+        <v>171.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="W37" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>49.8</v>
-      </c>
+      <c r="V37" s="15" t="n">
+        <v>1141.1</v>
+      </c>
+      <c r="W37" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>1181.2</v>
+        <v>188.2</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>92.2</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3618,66 +3624,64 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>442.2</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>443.3</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>30.4</v>
       </c>
-      <c r="E38" s="12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F38" s="12" t="n">
+      <c r="E38" s="9" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F38" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="G38" s="3" t="n">
-        <v>16.9</v>
+      <c r="G38" s="9" t="n">
+        <v>16.5</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>18.2</v>
+        <v>11.2</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K38" s="3" t="inlineStr"/>
+      <c r="L38" s="15" t="n">
         <v>16.8</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="15" t="n">
         <v>10.6</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>27.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>7.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>26.7</v>
       </c>
-      <c r="R38" s="9" t="n">
-        <v>14.8</v>
+      <c r="R38" s="15" t="n">
+        <v>14.5</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>2.3</v>
+        <v>9.5</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>20.3</v>
       </c>
-      <c r="U38" s="3" t="n">
+      <c r="U38" s="16" t="n">
         <v>26.9</v>
       </c>
-      <c r="V38" s="9" t="n">
+      <c r="V38" s="15" t="n">
         <v>22.8</v>
       </c>
-      <c r="W38" s="9" t="n">
+      <c r="W38" s="15" t="n">
         <v>13.4</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3703,40 +3707,40 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>914.6</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>18.66</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <v>81.09999999999999</v>
+        <v>5914.6</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F39" s="9" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="H39" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>8.9</v>
+        <v>17.9</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M39" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="M39" s="9" t="n">
         <v>10.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>9.4</v>
+        <v>0.9</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>21</v>
@@ -3744,7 +3748,7 @@
       <c r="P39" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q39" s="12" t="n">
+      <c r="Q39" s="9" t="n">
         <v>28.7</v>
       </c>
       <c r="R39" s="3" t="n">
@@ -3754,25 +3758,25 @@
         <v>10</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="U39" s="16" t="n">
         <v>29.4</v>
       </c>
-      <c r="V39" s="12" t="n">
+      <c r="V39" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="X39" s="16" t="n">
+      <c r="X39" s="3" t="n">
         <v>11.4</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>36.4</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>28.8</v>
+        <v>20.6</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3788,76 +3792,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>641.4</v>
-      </c>
-      <c r="D40" s="12" t="n">
+        <v>617.1</v>
+      </c>
+      <c r="D40" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="9" t="n">
         <v>16</v>
       </c>
       <c r="H40" s="16" t="n">
         <v>11.2</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="M40" s="3" t="n">
+      <c r="M40" s="9" t="n">
         <v>10.4</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>9.1</v>
+        <v>21.7</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="P40" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="Q40" s="12" t="n">
+      <c r="Q40" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R40" s="16" t="n">
+      <c r="R40" s="3" t="n">
         <v>15</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>19.2</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>84.2</v>
+        <v>94.2</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>26</v>
+        <v>26.8</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="16" t="n">
         <v>10.1</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>28</v>
+        <v>318</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.1</v>
+        <v>223.6</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3875,20 +3879,20 @@
       <c r="C41" s="3" t="n">
         <v>587.5</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E41" s="12" t="n">
+      <c r="D41" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E41" s="9" t="n">
         <v>16.2</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="G41" s="12" t="n">
+      <c r="F41" s="9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="G41" s="9" t="n">
         <v>15.2</v>
       </c>
-      <c r="H41" s="3" t="n">
-        <v>13</v>
+      <c r="H41" s="16" t="n">
+        <v>53</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>6.6</v>
@@ -3899,22 +3903,22 @@
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="L41" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="M41" s="16" t="n">
-        <v>11.9</v>
+      <c r="M41" s="9" t="n">
+        <v>11.1</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="P41" s="16" t="n">
         <v>10.8</v>
       </c>
-      <c r="Q41" s="12" t="n">
+      <c r="Q41" s="9" t="n">
         <v>29.8</v>
       </c>
       <c r="R41" s="3" t="n">
@@ -3924,23 +3928,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="U41" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="U41" s="16" t="n">
         <v>32.6</v>
       </c>
-      <c r="V41" s="12" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="X41" s="16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y41" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>128.9</v>
+      </c>
       <c r="Z41" s="3" t="n">
-        <v>0.2</v>
+        <v>26.4</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3958,17 +3964,17 @@
       <c r="C42" s="3" t="n">
         <v>481.1</v>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="9" t="n">
         <v>31.2</v>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="G42" s="16" t="n">
-        <v>18.8</v>
+      <c r="E42" s="9" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="F42" s="9" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>15.8</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>12</v>
@@ -3977,27 +3983,27 @@
         <v>5.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="L42" s="9" t="n">
         <v>16.8</v>
       </c>
-      <c r="M42" s="16" t="n">
+      <c r="M42" s="9" t="n">
         <v>10.9</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Q42" s="12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Q42" s="9" t="n">
         <v>26.4</v>
       </c>
       <c r="R42" s="3" t="n">
@@ -4007,24 +4013,26 @@
         <v>9.9</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>28.7</v>
+        <v>128.7</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="V42" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="W42" s="16" t="n">
-        <v>23</v>
+      <c r="V42" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="X42" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="Z42" s="3" t="inlineStr"/>
+        <v>1392</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -4039,22 +4047,22 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>534</v>
-      </c>
-      <c r="D43" s="12" t="n">
+        <v>234</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="E43" s="12" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>23.3</v>
-      </c>
-      <c r="G43" s="16" t="n">
-        <v>4.1</v>
+      <c r="E43" s="9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F43" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>14.1</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>83.40000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>5.9</v>
@@ -4063,24 +4071,24 @@
         <v>9.699999999999999</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L43" s="9" t="n">
         <v>17.7</v>
       </c>
-      <c r="M43" s="3" t="n">
+      <c r="M43" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Q43" s="12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q43" s="9" t="n">
         <v>28.9</v>
       </c>
       <c r="R43" s="3" t="n">
@@ -4090,16 +4098,16 @@
         <v>8.5</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="U43" s="3" t="n">
+        <v>121.8</v>
+      </c>
+      <c r="U43" s="16" t="n">
         <v>31.4</v>
       </c>
-      <c r="V43" s="12" t="n">
+      <c r="V43" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="X43" s="3" t="n">
         <v>8.4</v>
@@ -4108,7 +4116,7 @@
         <v>25.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>124.6</v>
+        <v>24.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4124,18 +4132,18 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="D44" s="12" t="n">
+        <v>258</v>
+      </c>
+      <c r="D44" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="E44" s="9" t="n">
         <v>15.1</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F44" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="G44" s="9" t="n">
         <v>15.7</v>
       </c>
       <c r="H44" s="3" t="n">
@@ -4148,51 +4156,53 @@
         <v>9</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L44" s="12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="L44" s="9" t="n">
         <v>16.6</v>
       </c>
-      <c r="M44" s="15" t="n">
-        <v>4.8</v>
+      <c r="M44" s="9" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="O44" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="P44" s="3" t="n">
+        <v>644</v>
+      </c>
+      <c r="P44" s="16" t="n">
         <v>10.6</v>
       </c>
-      <c r="Q44" s="12" t="n">
+      <c r="Q44" s="9" t="n">
         <v>29.2</v>
       </c>
-      <c r="R44" s="3" t="n">
+      <c r="R44" s="16" t="n">
         <v>14.4</v>
       </c>
       <c r="S44" s="3" t="n">
         <v>87.8</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>112.3</v>
+        <v>119.2</v>
       </c>
       <c r="U44" s="16" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="V44" s="12" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W44" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="X44" s="3" t="n">
-        <v>0.1</v>
+      <c r="X44" s="16" t="n">
+        <v>227.9</v>
       </c>
       <c r="Y44" s="3" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>290.8</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>112.4</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4207,72 +4217,72 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1801.1</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>1122.1</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>91.59999999999999</v>
+        <v>2312.2</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>21.7</v>
+        <v>7194.9</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>721.1</v>
+        <v>85</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>52.3</v>
       </c>
-      <c r="K45" s="9" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>1281.8</v>
-      </c>
-      <c r="M45" s="9" t="n">
-        <v>80.09999999999999</v>
+      <c r="K45" s="15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L45" s="15" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="M45" s="15" t="n">
+        <v>1202.9</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>27.1</v>
+        <v>2.7</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>1226.5</v>
+        <v>226.5</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>28.4</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>81.5</v>
+        <v>2908.4</v>
+      </c>
+      <c r="Q45" s="15" t="n">
+        <v>178</v>
+      </c>
+      <c r="R45" s="15" t="n">
+        <v>182.8</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>180</v>
+        <v>182.8</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>126.4</v>
-      </c>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="9" t="n">
-        <v>144.2</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>28.8</v>
+        <v>136.9</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="V45" s="15" t="n">
+        <v>146.2</v>
+      </c>
+      <c r="W45" s="15" t="n">
+        <v>286.2</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y45" s="3" t="n">
-        <v>1222.9</v>
-      </c>
+        <v>164.7</v>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
       <c r="Z45" s="3" t="inlineStr"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4288,76 +4298,74 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>561.8</v>
-      </c>
-      <c r="D46" s="15" t="n">
-        <v>40.6</v>
+        <v>551.8</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>29.3</v>
       </c>
       <c r="E46" s="9" t="n">
         <v>15.3</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>33</v>
+        <v>22.3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L46" s="12" t="n">
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="9" t="n">
         <v>16.8</v>
       </c>
       <c r="M46" s="9" t="n">
-        <v>80.8</v>
+        <v>10.8</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>49.4</v>
+        <v>149.4</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="Q46" s="12" t="n">
+      <c r="Q46" s="9" t="n">
         <v>28.8</v>
       </c>
-      <c r="R46" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="S46" s="3" t="n">
-        <v>9</v>
+      <c r="R46" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>39</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="U46" s="3" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="W46" s="9" t="n">
+      <c r="U46" s="16" t="n">
+        <v>390.8</v>
+      </c>
+      <c r="V46" s="15" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="W46" s="15" t="n">
         <v>12.4</v>
       </c>
-      <c r="X46" s="3" t="n">
+      <c r="X46" s="16" t="n">
         <v>16.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>22.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>112.6</v>
+        <v>119.6</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/501/501_197210_SF.JPG_stage_recheck_temp_thresholds.xlsx
@@ -1212,7 +1212,7 @@
       <c r="J9" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1376,7 +1376,7 @@
       <c r="J11" s="3" t="n">
         <v>6.8</v>
       </c>
-      <c r="K11" s="3" t="n"/>
+      <c r="K11" s="13" t="n"/>
       <c r="L11" s="3" t="n">
         <v>18.2</v>
       </c>
@@ -1794,7 +1794,7 @@
       <c r="J16" s="3" t="n">
         <v>36.2</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>11.7</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -2372,7 +2372,7 @@
       <c r="J23" s="3" t="n">
         <v>57.2</v>
       </c>
-      <c r="K23" s="3" t="n"/>
+      <c r="K23" s="10" t="n"/>
       <c r="L23" s="3" t="n">
         <v>2.2</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>16.1</v>
       </c>
       <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
+      <c r="K25" s="13" t="n"/>
       <c r="L25" s="3" t="n">
         <v>19.8</v>
       </c>
@@ -2697,7 +2697,7 @@
       <c r="J27" s="8" t="n">
         <v>10.4</v>
       </c>
-      <c r="K27" s="3" t="n"/>
+      <c r="K27" s="13" t="n"/>
       <c r="L27" s="3" t="n">
         <v>16.3</v>
       </c>
@@ -2946,7 +2946,7 @@
       <c r="J30" s="3" t="n">
         <v>35.8</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="9" t="n">
         <v>81.8</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3529,7 +3529,7 @@
       <c r="J37" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="K37" s="3" t="n"/>
+      <c r="K37" s="10" t="n"/>
       <c r="L37" s="3" t="n">
         <v>82.90000000000001</v>
       </c>
@@ -3695,7 +3695,7 @@
       <c r="J39" s="3" t="n">
         <v>61.4</v>
       </c>
-      <c r="K39" s="3" t="n"/>
+      <c r="K39" s="13" t="n"/>
       <c r="L39" s="3" t="n">
         <v>16.8</v>
       </c>
@@ -4201,7 +4201,7 @@
       <c r="J45" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="9" t="n">
         <v>3.5</v>
       </c>
       <c r="L45" s="3" t="n">
